--- a/Fantasy unificado/roster.xlsx
+++ b/Fantasy unificado/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Unificar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1187" documentId="8_{32D250B9-44B0-4D6A-89C9-E8E8B0ED30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98A9FAAB-79FD-4040-A383-BC3CF6F16627}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62FFA30F-5A49-4041-9C0E-7735BFB4A2F2}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="1" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="524">
   <si>
     <t>player_id</t>
   </si>
@@ -1608,6 +1608,21 @@
   </si>
   <si>
     <t>J7R2S2526</t>
+  </si>
+  <si>
+    <t>SF/PF</t>
+  </si>
+  <si>
+    <t>PF/C</t>
+  </si>
+  <si>
+    <t>Clint Capela</t>
+  </si>
+  <si>
+    <t>PG/SG</t>
+  </si>
+  <si>
+    <t>SG/SF</t>
   </si>
 </sst>
 </file>
@@ -1667,12 +1682,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2012,7 +2030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDFA625-895D-46B5-9149-0741A5E1C2FB}">
-  <dimension ref="A1:M416"/>
+  <dimension ref="A1:M417"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -2264,7 +2282,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1">
         <v>20.399999999999999</v>
@@ -2490,7 +2508,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E15" s="1">
         <v>22.5</v>
@@ -2523,7 +2541,7 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E16" s="1">
         <v>21.8</v>
@@ -2589,7 +2607,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E18" s="1">
         <v>27.6</v>
@@ -2653,7 +2671,7 @@
         <v>44</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E20" s="1">
         <v>18.2</v>
@@ -2750,7 +2768,7 @@
         <v>47</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E23" s="1">
         <v>17.100000000000001</v>
@@ -3073,7 +3091,7 @@
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E33" s="1">
         <v>17</v>
@@ -3169,7 +3187,7 @@
         <v>60</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>519</v>
       </c>
       <c r="E36" s="1">
         <v>18.3</v>
@@ -3202,7 +3220,7 @@
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E37" s="1">
         <v>33.5</v>
@@ -3331,7 +3349,7 @@
         <v>65</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E41" s="1">
         <v>18.100000000000001</v>
@@ -3491,7 +3509,7 @@
         <v>70</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E46" s="1">
         <v>12</v>
@@ -3523,7 +3541,7 @@
         <v>71</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="E47" s="1">
         <v>11.8</v>
@@ -3588,7 +3606,7 @@
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E49" s="1">
         <v>24.2</v>
@@ -3652,7 +3670,7 @@
         <v>75</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E51" s="1">
         <v>14.2</v>
@@ -3749,7 +3767,7 @@
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E54" s="1">
         <v>28.7</v>
@@ -3781,7 +3799,7 @@
         <v>79</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E55" s="1">
         <v>26.7</v>
@@ -3814,7 +3832,7 @@
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E56" s="1">
         <v>24.2</v>
@@ -3942,7 +3960,7 @@
         <v>84</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E60" s="1">
         <v>11.9</v>
@@ -4006,7 +4024,7 @@
         <v>86</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E62" s="1">
         <v>21</v>
@@ -4166,7 +4184,7 @@
         <v>91</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E67" s="1">
         <v>24</v>
@@ -4231,7 +4249,7 @@
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E69" s="1">
         <v>27.9</v>
@@ -4263,7 +4281,7 @@
         <v>94</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E70" s="1">
         <v>13.7</v>
@@ -4327,7 +4345,7 @@
         <v>96</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E72" s="1">
         <v>10.5</v>
@@ -4392,7 +4410,7 @@
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E74" s="1">
         <v>20.9</v>
@@ -4424,7 +4442,7 @@
         <v>99</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E75" s="1">
         <v>10.5</v>
@@ -4488,7 +4506,7 @@
         <v>101</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E77" s="1">
         <v>13.6</v>
@@ -4521,7 +4539,7 @@
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E78" s="1">
         <v>17.100000000000001</v>
@@ -4714,7 +4732,7 @@
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E84" s="1">
         <v>21.5</v>
@@ -4780,7 +4798,7 @@
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1" t="s">
-        <v>21</v>
+        <v>520</v>
       </c>
       <c r="E86" s="1">
         <v>19.399999999999999</v>
@@ -4844,7 +4862,7 @@
         <v>112</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E88" s="1">
         <v>10.6</v>
@@ -4941,7 +4959,7 @@
         <v>115</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E91" s="1">
         <v>20</v>
@@ -5135,7 +5153,7 @@
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E97" s="1">
         <v>26</v>
@@ -5200,7 +5218,7 @@
         <v>123</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E99" s="1">
         <v>8.4</v>
@@ -5328,7 +5346,7 @@
         <v>127</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E103" s="1">
         <v>16.7</v>
@@ -5360,7 +5378,7 @@
         <v>128</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E104" s="1">
         <v>15.2</v>
@@ -5392,7 +5410,7 @@
         <v>129</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E105" s="1">
         <v>13.2</v>
@@ -5488,7 +5506,7 @@
         <v>132</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E108" s="1">
         <v>19.3</v>
@@ -5552,7 +5570,7 @@
         <v>134</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>22</v>
+        <v>523</v>
       </c>
       <c r="E110" s="1">
         <v>17.3</v>
@@ -5585,7 +5603,7 @@
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E111" s="1">
         <v>16.7</v>
@@ -5617,7 +5635,7 @@
         <v>136</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E112" s="1">
         <v>13.6</v>
@@ -5714,7 +5732,7 @@
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E115" s="1">
         <v>20.6</v>
@@ -5746,7 +5764,7 @@
         <v>140</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E116" s="1">
         <v>17.399999999999999</v>
@@ -5811,7 +5829,7 @@
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E118" s="1">
         <v>16.7</v>
@@ -5875,7 +5893,7 @@
         <v>144</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E120" s="1">
         <v>14.8</v>
@@ -5907,7 +5925,7 @@
         <v>145</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E121" s="1">
         <v>13.8</v>
@@ -5971,7 +5989,7 @@
         <v>147</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E123" s="1">
         <v>13.3</v>
@@ -6003,7 +6021,7 @@
         <v>148</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E124" s="1">
         <v>13.2</v>
@@ -6164,7 +6182,7 @@
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E129" s="1">
         <v>28.8</v>
@@ -6196,7 +6214,7 @@
         <v>154</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E130" s="1">
         <v>15.4</v>
@@ -6228,7 +6246,7 @@
         <v>155</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E131" s="1">
         <v>14.1</v>
@@ -6421,7 +6439,7 @@
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E137" s="1">
         <v>20.2</v>
@@ -6614,7 +6632,7 @@
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E143" s="1">
         <v>24.7</v>
@@ -6647,7 +6665,7 @@
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E144" s="1">
         <v>23.6</v>
@@ -6745,7 +6763,7 @@
         <v>171</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E147" s="1">
         <v>15.4</v>
@@ -6777,7 +6795,7 @@
         <v>172</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E148" s="1">
         <v>12</v>
@@ -6809,7 +6827,7 @@
         <v>173</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E149" s="1">
         <v>9.8000000000000007</v>
@@ -6874,7 +6892,7 @@
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E151" s="1">
         <v>23.3</v>
@@ -6970,7 +6988,7 @@
         <v>178</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>25</v>
+        <v>519</v>
       </c>
       <c r="E154" s="1">
         <v>17.100000000000001</v>
@@ -7099,7 +7117,7 @@
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E158" s="1">
         <v>27.9</v>
@@ -7131,7 +7149,7 @@
         <v>183</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E159" s="1">
         <v>13</v>
@@ -7195,7 +7213,7 @@
         <v>185</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E161" s="1">
         <v>25.4</v>
@@ -7259,7 +7277,7 @@
         <v>187</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E163" s="1">
         <v>16.5</v>
@@ -7387,7 +7405,7 @@
         <v>191</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E167" s="1">
         <v>31.1</v>
@@ -7420,7 +7438,7 @@
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E168" s="1">
         <v>20.8</v>
@@ -7452,7 +7470,7 @@
         <v>193</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="E169" s="1">
         <v>12.5</v>
@@ -7484,7 +7502,7 @@
         <v>194</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E170" s="1">
         <v>11.7</v>
@@ -7516,7 +7534,7 @@
         <v>195</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E171" s="1">
         <v>14.8</v>
@@ -7548,7 +7566,7 @@
         <v>196</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E172" s="1">
         <v>13.8</v>
@@ -7709,7 +7727,7 @@
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E177" s="1">
         <v>28.3</v>
@@ -7741,7 +7759,7 @@
         <v>202</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E178" s="1">
         <v>20.100000000000001</v>
@@ -7773,7 +7791,7 @@
         <v>203</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E179" s="1">
         <v>13.7</v>
@@ -7869,7 +7887,7 @@
         <v>206</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E182" s="1">
         <v>12.2</v>
@@ -7965,7 +7983,7 @@
         <v>209</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E185" s="1">
         <v>16.399999999999999</v>
@@ -8029,7 +8047,7 @@
         <v>211</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E187" s="1">
         <v>13.9</v>
@@ -8286,7 +8304,7 @@
       </c>
       <c r="C195" s="1"/>
       <c r="D195" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E195" s="1">
         <v>26.1</v>
@@ -8318,7 +8336,7 @@
         <v>220</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E196" s="1">
         <v>17</v>
@@ -8350,7 +8368,7 @@
         <v>221</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E197" s="1">
         <v>13.8</v>
@@ -8606,7 +8624,7 @@
         <v>229</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E205" s="1">
         <v>15</v>
@@ -8638,7 +8656,7 @@
         <v>230</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E206" s="1">
         <v>14.4</v>
@@ -8670,7 +8688,7 @@
         <v>231</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E207" s="1">
         <v>12.2</v>
@@ -8831,7 +8849,7 @@
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E212" s="1">
         <v>23.6</v>
@@ -8895,7 +8913,7 @@
         <v>238</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>23</v>
+        <v>523</v>
       </c>
       <c r="E214" s="1">
         <v>10.199999999999999</v>
@@ -9120,7 +9138,7 @@
         <v>245</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E221" s="1">
         <v>13.4</v>
@@ -9313,7 +9331,7 @@
         <v>251</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E227" s="1">
         <v>19</v>
@@ -9346,7 +9364,7 @@
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E228" s="1">
         <v>18.600000000000001</v>
@@ -9666,7 +9684,7 @@
         <v>262</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E238" s="1">
         <v>20.8</v>
@@ -9699,7 +9717,7 @@
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E239" s="1">
         <v>17.399999999999999</v>
@@ -9795,7 +9813,7 @@
         <v>266</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E242" s="1">
         <v>11.8</v>
@@ -10019,7 +10037,7 @@
         <v>273</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E249" s="1">
         <v>18.7</v>
@@ -11268,7 +11286,7 @@
       </c>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E288" s="1">
         <v>18.399999999999999</v>
@@ -11300,7 +11318,7 @@
         <v>313</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E289" s="1">
         <v>13.5</v>
@@ -11524,7 +11542,7 @@
         <v>320</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E296" s="1">
         <v>19.2</v>
@@ -11620,7 +11638,7 @@
         <v>323</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="E299" s="1">
         <v>9.9</v>
@@ -11684,7 +11702,7 @@
         <v>325</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="E301" s="1">
         <v>9.1999999999999993</v>
@@ -12132,7 +12150,7 @@
         <v>339</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E315" s="1">
         <v>7.4</v>
@@ -12228,7 +12246,7 @@
         <v>342</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E318" s="1">
         <v>14.3</v>
@@ -12837,7 +12855,7 @@
         <v>361</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E337" s="1">
         <v>15.4</v>
@@ -12901,7 +12919,7 @@
         <v>363</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E339" s="1">
         <v>10.199999999999999</v>
@@ -13125,7 +13143,7 @@
         <v>370</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E346" s="1">
         <v>7.6</v>
@@ -13701,7 +13719,7 @@
         <v>388</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E364" s="1">
         <v>13.4</v>
@@ -13925,7 +13943,7 @@
         <v>395</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>24</v>
+        <v>522</v>
       </c>
       <c r="E371" s="1">
         <v>6.3</v>
@@ -14021,7 +14039,7 @@
         <v>398</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E374" s="1">
         <v>12.5</v>
@@ -14245,7 +14263,7 @@
         <v>405</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>25</v>
+        <v>522</v>
       </c>
       <c r="E381" s="1">
         <v>8.6</v>
@@ -14981,7 +14999,7 @@
         <v>428</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="E404" s="1">
         <v>8.1999999999999993</v>
@@ -15386,6 +15404,38 @@
         <v>0</v>
       </c>
       <c r="K416" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E417" s="1">
+        <v>0</v>
+      </c>
+      <c r="F417" s="1">
+        <v>0</v>
+      </c>
+      <c r="G417" s="1">
+        <v>0</v>
+      </c>
+      <c r="H417" s="1">
+        <v>0</v>
+      </c>
+      <c r="I417" s="1">
+        <v>0</v>
+      </c>
+      <c r="J417" s="1">
+        <v>0</v>
+      </c>
+      <c r="K417" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15950,10 +16000,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19E893F-F6CA-495F-B37D-0D5DEFFEED8B}">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -15970,7 +16020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7</v>
       </c>
@@ -15983,8 +16033,12 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="str">
+        <f>VLOOKUP(B2,players!A:B,2)</f>
+        <v>Anthony Davis</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7</v>
       </c>
@@ -15997,8 +16051,12 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="str">
+        <f>VLOOKUP(B3,players!A:B,2)</f>
+        <v>Kel'el Ware</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>7</v>
       </c>
@@ -16011,8 +16069,12 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="str">
+        <f>VLOOKUP(B4,players!A:B,2)</f>
+        <v>Ausar Thompson</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
@@ -16025,8 +16087,12 @@
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="str">
+        <f>VLOOKUP(B5,players!A:B,2)</f>
+        <v>Ja Morant</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7</v>
       </c>
@@ -16039,8 +16105,12 @@
       <c r="D6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="str">
+        <f>VLOOKUP(B6,players!A:B,2)</f>
+        <v>Scottie Barnes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -16053,8 +16123,12 @@
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="str">
+        <f>VLOOKUP(B7,players!A:B,2)</f>
+        <v>Dejounte Murray</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -16067,8 +16141,12 @@
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="str">
+        <f>VLOOKUP(B8,players!A:B,2)</f>
+        <v>Onyeka Okongwu</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -16081,8 +16159,12 @@
       <c r="D9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="str">
+        <f>VLOOKUP(B9,players!A:B,2)</f>
+        <v>Matas Buzelis</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -16095,8 +16177,12 @@
       <c r="D10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="str">
+        <f>VLOOKUP(B10,players!A:B,2)</f>
+        <v>Anthony Edwards</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -16109,8 +16195,12 @@
       <c r="D11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="str">
+        <f>VLOOKUP(B11,players!A:B,2)</f>
+        <v>Tyrese Maxey</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
@@ -16123,8 +16213,12 @@
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="str">
+        <f>VLOOKUP(B12,players!A:B,2)</f>
+        <v>Donte DiVincenzo</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
@@ -16137,8 +16231,12 @@
       <c r="D13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="str">
+        <f>VLOOKUP(B13,players!A:B,2)</f>
+        <v>Mikal Bridges</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -16151,8 +16249,12 @@
       <c r="D14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="str">
+        <f>VLOOKUP(B14,players!A:B,2)</f>
+        <v>Alperen Şengün</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -16165,8 +16267,12 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="str">
+        <f>VLOOKUP(B15,players!A:B,2)</f>
+        <v>Kevin Durant</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
@@ -16179,13 +16285,17 @@
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F16" t="str">
+        <f>VLOOKUP(B16,players!A:B,2)</f>
+        <v>Brandon Miller</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="B17">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>438</v>
@@ -16193,8 +16303,12 @@
       <c r="D17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F17" t="str">
+        <f>VLOOKUP(B17,players!A:B,2)</f>
+        <v>Jalen Green</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -16207,8 +16321,12 @@
       <c r="D18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F18" t="str">
+        <f>VLOOKUP(B18,players!A:B,2)</f>
+        <v>Tyler Herro</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -16221,8 +16339,12 @@
       <c r="D19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F19" t="str">
+        <f>VLOOKUP(B19,players!A:B,2)</f>
+        <v>Trae Young</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3</v>
       </c>
@@ -16235,8 +16357,12 @@
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F20" t="str">
+        <f>VLOOKUP(B20,players!A:B,2)</f>
+        <v>Jalen Duren</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -16249,8 +16375,12 @@
       <c r="D21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F21" t="str">
+        <f>VLOOKUP(B21,players!A:B,2)</f>
+        <v>Luka Dončić</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3</v>
       </c>
@@ -16263,8 +16393,12 @@
       <c r="D22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F22" t="str">
+        <f>VLOOKUP(B22,players!A:B,2)</f>
+        <v>Kawhi Leonard</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3</v>
       </c>
@@ -16277,8 +16411,12 @@
       <c r="D23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" t="str">
+        <f>VLOOKUP(B23,players!A:B,2)</f>
+        <v>Jaren Jackson Jr.</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3</v>
       </c>
@@ -16291,8 +16429,12 @@
       <c r="D24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F24" t="str">
+        <f>VLOOKUP(B24,players!A:B,2)</f>
+        <v>OG Anunoby</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -16305,8 +16447,12 @@
       <c r="D25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F25" t="str">
+        <f>VLOOKUP(B25,players!A:B,2)</f>
+        <v>Kyrie Irving</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -16319,8 +16465,12 @@
       <c r="D26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F26" t="str">
+        <f>VLOOKUP(B26,players!A:B,2)</f>
+        <v>Bam Adebayo</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -16333,8 +16483,12 @@
       <c r="D27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F27" t="str">
+        <f>VLOOKUP(B27,players!A:B,2)</f>
+        <v>Jaylen Brown</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -16347,8 +16501,12 @@
       <c r="D28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F28" t="str">
+        <f>VLOOKUP(B28,players!A:B,2)</f>
+        <v>Stephon Castle</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4</v>
       </c>
@@ -16361,8 +16519,12 @@
       <c r="D29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F29" t="str">
+        <f>VLOOKUP(B29,players!A:B,2)</f>
+        <v>Franz Wagner</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
@@ -16375,8 +16537,12 @@
       <c r="D30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F30" t="str">
+        <f>VLOOKUP(B30,players!A:B,2)</f>
+        <v>Donovan Mitchell</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4</v>
       </c>
@@ -16389,8 +16555,12 @@
       <c r="D31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F31" t="str">
+        <f>VLOOKUP(B31,players!A:B,2)</f>
+        <v>DeMar DeRozan</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -16403,8 +16573,12 @@
       <c r="D32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F32" t="str">
+        <f>VLOOKUP(B32,players!A:B,2)</f>
+        <v>Joel Embiid</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>5</v>
       </c>
@@ -16417,8 +16591,12 @@
       <c r="D33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F33" t="str">
+        <f>VLOOKUP(B33,players!A:B,2)</f>
+        <v>Giannis Antetokounmpo</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -16431,13 +16609,17 @@
       <c r="D34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F34" t="str">
+        <f>VLOOKUP(B34,players!A:B,2)</f>
+        <v>VJ Edgecombe</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35">
-        <v>219</v>
+        <v>143</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>25</v>
@@ -16445,8 +16627,12 @@
       <c r="D35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F35" t="str">
+        <f>VLOOKUP(B35,players!A:B,2)</f>
+        <v>James Harden</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -16459,13 +16645,17 @@
       <c r="D36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F36" t="str">
+        <f>VLOOKUP(B36,players!A:B,2)</f>
+        <v>Michael Porter Jr.</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
       <c r="B37">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>24</v>
@@ -16473,8 +16663,12 @@
       <c r="D37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F37" t="str">
+        <f>VLOOKUP(B37,players!A:B,2)</f>
+        <v>Naz Reid</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>6</v>
       </c>
@@ -16487,8 +16681,12 @@
       <c r="D38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F38" t="str">
+        <f>VLOOKUP(B38,players!A:B,2)</f>
+        <v>Nikola Jokić</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6</v>
       </c>
@@ -16501,8 +16699,12 @@
       <c r="D39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F39" t="str">
+        <f>VLOOKUP(B39,players!A:B,2)</f>
+        <v>Paolo Banchero</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -16515,8 +16717,12 @@
       <c r="D40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F40" t="str">
+        <f>VLOOKUP(B40,players!A:B,2)</f>
+        <v>Miles Bridges</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>6</v>
       </c>
@@ -16529,8 +16735,12 @@
       <c r="D41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F41" t="str">
+        <f>VLOOKUP(B41,players!A:B,2)</f>
+        <v>Cade Cunningham</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>6</v>
       </c>
@@ -16543,8 +16753,12 @@
       <c r="D42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F42" t="str">
+        <f>VLOOKUP(B42,players!A:B,2)</f>
+        <v>Derrick White</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
@@ -16557,13 +16771,17 @@
       <c r="D43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F43" t="str">
+        <f>VLOOKUP(B43,players!A:B,2)</f>
+        <v>Keyonte George</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>21</v>
@@ -16571,8 +16789,12 @@
       <c r="D44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F44" t="str">
+        <f>VLOOKUP(B44,players!A:B,2)</f>
+        <v>Donovan Clingan</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -16585,8 +16807,12 @@
       <c r="D45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F45" t="str">
+        <f>VLOOKUP(B45,players!A:B,2)</f>
+        <v>Jalen Johnson</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8</v>
       </c>
@@ -16599,8 +16825,12 @@
       <c r="D46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F46" t="str">
+        <f>VLOOKUP(B46,players!A:B,2)</f>
+        <v>Trey Murphy III</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>8</v>
       </c>
@@ -16613,8 +16843,12 @@
       <c r="D47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F47" t="str">
+        <f>VLOOKUP(B47,players!A:B,2)</f>
+        <v>Zion Williamson</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>8</v>
       </c>
@@ -16627,8 +16861,12 @@
       <c r="D48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F48" t="str">
+        <f>VLOOKUP(B48,players!A:B,2)</f>
+        <v>De'Aaron Fox</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>8</v>
       </c>
@@ -16641,8 +16879,12 @@
       <c r="D49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F49" t="str">
+        <f>VLOOKUP(B49,players!A:B,2)</f>
+        <v>Norman Powell</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9</v>
       </c>
@@ -16655,8 +16897,12 @@
       <c r="D50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F50" t="str">
+        <f>VLOOKUP(B50,players!A:B,2)</f>
+        <v>Jayson Tatum</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>9</v>
       </c>
@@ -16669,8 +16915,12 @@
       <c r="D51">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F51" t="str">
+        <f>VLOOKUP(B51,players!A:B,2)</f>
+        <v>Jarrett Allen</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9</v>
       </c>
@@ -16683,8 +16933,12 @@
       <c r="D52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F52" t="str">
+        <f>VLOOKUP(B52,players!A:B,2)</f>
+        <v>Brandon Ingram</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>9</v>
       </c>
@@ -16697,8 +16951,12 @@
       <c r="D53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F53" t="str">
+        <f>VLOOKUP(B53,players!A:B,2)</f>
+        <v>Shaedon Sharpe</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>9</v>
       </c>
@@ -16711,8 +16969,12 @@
       <c r="D54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F54" t="str">
+        <f>VLOOKUP(B54,players!A:B,2)</f>
+        <v>Stephen Curry</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9</v>
       </c>
@@ -16725,8 +16987,12 @@
       <c r="D55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F55" t="str">
+        <f>VLOOKUP(B55,players!A:B,2)</f>
+        <v>Darius Garland</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>10</v>
       </c>
@@ -16739,8 +17005,12 @@
       <c r="D56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F56" t="str">
+        <f>VLOOKUP(B56,players!A:B,2)</f>
+        <v>Nikola Vučević</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>10</v>
       </c>
@@ -16753,8 +17023,12 @@
       <c r="D57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F57" t="str">
+        <f>VLOOKUP(B57,players!A:B,2)</f>
+        <v>Alex Sarr</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>10</v>
       </c>
@@ -16767,8 +17041,12 @@
       <c r="D58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F58" t="str">
+        <f>VLOOKUP(B58,players!A:B,2)</f>
+        <v>Julius Randle</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>10</v>
       </c>
@@ -16781,8 +17059,12 @@
       <c r="D59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F59" t="str">
+        <f>VLOOKUP(B59,players!A:B,2)</f>
+        <v>Jalen Williams</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>10</v>
       </c>
@@ -16795,8 +17077,12 @@
       <c r="D60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F60" t="str">
+        <f>VLOOKUP(B60,players!A:B,2)</f>
+        <v>Jamal Murray</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>10</v>
       </c>
@@ -16809,8 +17095,12 @@
       <c r="D61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F61" t="str">
+        <f>VLOOKUP(B61,players!A:B,2)</f>
+        <v>Jalen Brunson</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>11</v>
       </c>
@@ -16823,8 +17113,12 @@
       <c r="D62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F62" t="str">
+        <f>VLOOKUP(B62,players!A:B,2)</f>
+        <v>Domantas Sabonis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>11</v>
       </c>
@@ -16837,8 +17131,12 @@
       <c r="D63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F63" t="str">
+        <f>VLOOKUP(B63,players!A:B,2)</f>
+        <v>Desmond Bane</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>11</v>
       </c>
@@ -16851,8 +17149,12 @@
       <c r="D64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F64" t="str">
+        <f>VLOOKUP(B64,players!A:B,2)</f>
+        <v>Amen Thompson</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>11</v>
       </c>
@@ -16865,8 +17167,12 @@
       <c r="D65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F65" t="str">
+        <f>VLOOKUP(B65,players!A:B,2)</f>
+        <v>Shai Gilgeous-Alexander</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>11</v>
       </c>
@@ -16879,8 +17185,12 @@
       <c r="D66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F66" t="str">
+        <f>VLOOKUP(B66,players!A:B,2)</f>
+        <v>CJ McCollum</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>11</v>
       </c>
@@ -16893,8 +17203,12 @@
       <c r="D67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F67" t="str">
+        <f>VLOOKUP(B67,players!A:B,2)</f>
+        <v>Paul George</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>12</v>
       </c>
@@ -16907,8 +17221,12 @@
       <c r="D68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F68" t="str">
+        <f>VLOOKUP(B68,players!A:B,2)</f>
+        <v>Chet Holmgren</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>12</v>
       </c>
@@ -16921,8 +17239,12 @@
       <c r="D69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F69" t="str">
+        <f>VLOOKUP(B69,players!A:B,2)</f>
+        <v>Lauri Markkanen</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>12</v>
       </c>
@@ -16935,8 +17257,12 @@
       <c r="D70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F70" t="str">
+        <f>VLOOKUP(B70,players!A:B,2)</f>
+        <v>Devin Booker</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>12</v>
       </c>
@@ -16949,8 +17275,12 @@
       <c r="D71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F71" t="str">
+        <f>VLOOKUP(B71,players!A:B,2)</f>
+        <v>Tyrese Haliburton</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>12</v>
       </c>
@@ -16963,8 +17293,12 @@
       <c r="D72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F72" t="str">
+        <f>VLOOKUP(B72,players!A:B,2)</f>
+        <v>Brandin Podziemski</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>12</v>
       </c>
@@ -16977,8 +17311,12 @@
       <c r="D73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F73" t="str">
+        <f>VLOOKUP(B73,players!A:B,2)</f>
+        <v>Kevin Porter Jr.</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>13</v>
       </c>
@@ -16991,8 +17329,12 @@
       <c r="D74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F74" t="str">
+        <f>VLOOKUP(B74,players!A:B,2)</f>
+        <v>Victor Wembanyama</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>13</v>
       </c>
@@ -17005,8 +17347,12 @@
       <c r="D75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F75" t="str">
+        <f>VLOOKUP(B75,players!A:B,2)</f>
+        <v>Josh Giddey</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>13</v>
       </c>
@@ -17019,8 +17365,12 @@
       <c r="D76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F76" t="str">
+        <f>VLOOKUP(B76,players!A:B,2)</f>
+        <v>Deni Avdija</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>13</v>
       </c>
@@ -17033,8 +17383,12 @@
       <c r="D77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F77" t="str">
+        <f>VLOOKUP(B77,players!A:B,2)</f>
+        <v>Pascal Siakam</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>13</v>
       </c>
@@ -17047,8 +17401,12 @@
       <c r="D78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F78" t="str">
+        <f>VLOOKUP(B78,players!A:B,2)</f>
+        <v>Andrew Nembhard</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>13</v>
       </c>
@@ -17061,8 +17419,12 @@
       <c r="D79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F79" t="str">
+        <f>VLOOKUP(B79,players!A:B,2)</f>
+        <v>Austin Reaves</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>14</v>
       </c>
@@ -17075,8 +17437,12 @@
       <c r="D80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F80" t="str">
+        <f>VLOOKUP(B80,players!A:B,2)</f>
+        <v>Evan Mobley</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>14</v>
       </c>
@@ -17089,8 +17455,12 @@
       <c r="D81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F81" t="str">
+        <f>VLOOKUP(B81,players!A:B,2)</f>
+        <v>LeBron James</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>14</v>
       </c>
@@ -17103,8 +17473,12 @@
       <c r="D82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F82" t="str">
+        <f>VLOOKUP(B82,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>14</v>
       </c>
@@ -17117,8 +17491,12 @@
       <c r="D83">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F83" t="str">
+        <f>VLOOKUP(B83,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>14</v>
       </c>
@@ -17131,8 +17509,12 @@
       <c r="D84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F84" t="str">
+        <f>VLOOKUP(B84,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>14</v>
       </c>
@@ -17144,6 +17526,10 @@
       </c>
       <c r="D85">
         <v>1</v>
+      </c>
+      <c r="F85" t="str">
+        <f>VLOOKUP(B85,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
       </c>
     </row>
   </sheetData>
@@ -17153,17 +17539,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E67E5-331D-4CC3-B636-B44F8A41C81C}">
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" style="2" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="2" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" hidden="1" customWidth="1"/>
@@ -17723,17 +18109,17 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Cam Spencer</v>
+        <v>Jay Huff</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -17741,14 +18127,23 @@
         <v>2</v>
       </c>
       <c r="B29">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Alperen Şengün</v>
+        <v>Cam Spencer</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -17756,14 +18151,23 @@
         <v>2</v>
       </c>
       <c r="B30">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>23500000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>23500000</v>
+      </c>
+      <c r="H30" s="2">
+        <v>23500000</v>
       </c>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Kevin Durant</v>
+        <v>Alperen Şengün</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -17771,14 +18175,17 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D31" s="2">
+        <v>15000000</v>
       </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Brandon Miller</v>
+        <v>Kevin Durant</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -17786,14 +18193,17 @@
         <v>2</v>
       </c>
       <c r="B32">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <v>9000000</v>
       </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Brandon Miller</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -17801,14 +18211,23 @@
         <v>2</v>
       </c>
       <c r="B33">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D33" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="F33" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H33" s="2">
+        <v>7000000</v>
       </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
-        <v>Tyler Herro</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -17816,14 +18235,20 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D34" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F34" s="2">
+        <v>6000000</v>
       </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>Trae Young</v>
+        <v>Tyler Herro</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -17831,14 +18256,23 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D35" s="2">
+        <v>21500000</v>
+      </c>
+      <c r="F35" s="2">
+        <v>21500000</v>
+      </c>
+      <c r="H35" s="2">
+        <v>21500000</v>
       </c>
       <c r="L35" t="str">
         <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>Russell Westbrook</v>
+        <v>Trae Young</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -17846,14 +18280,14 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Russell Westbrook</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -17861,14 +18295,29 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H37" s="2">
+        <v>3700000</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Derik Queen</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -17876,14 +18325,23 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H38" s="2">
+        <v>3100000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Zach Edey</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -17891,29 +18349,50 @@
         <v>2</v>
       </c>
       <c r="B39">
-        <v>290</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D39" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F39" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Will Riley</v>
+        <v>Zach Edey</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H40" s="2">
+        <v>1000000</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Will Riley</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -17921,14 +18400,20 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="F41" s="2">
+        <v>8000000</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -17936,14 +18421,14 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -17951,14 +18436,14 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -17966,14 +18451,17 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D44" s="2">
+        <v>5000000</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -17981,14 +18469,14 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -17996,14 +18484,14 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -18011,14 +18499,14 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -18026,14 +18514,23 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C48">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D48" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F48" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H48" s="2">
+        <v>40000000</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -18041,14 +18538,17 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D49" s="2">
+        <v>6000000</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -18056,14 +18556,20 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D50" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="F50" s="2">
+        <v>14000000</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -18071,44 +18577,59 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D51" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="F51" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="H51" s="2">
+        <v>6500000</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52">
-        <v>379</v>
+        <v>142</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D52" s="2">
+        <v>5000000</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53">
-        <v>364</v>
+        <v>295</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="D53" s="2">
+        <v>8000000</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -18116,14 +18637,29 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>104</v>
+        <v>379</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H54" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -18131,14 +18667,23 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>62</v>
+        <v>364</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -18146,14 +18691,14 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -18161,14 +18706,17 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2500000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -18176,14 +18724,17 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="D58" s="2">
+        <v>11000000</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -18191,14 +18742,20 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D59" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F59" s="2">
+        <v>5000000</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -18206,14 +18763,20 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="C60">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D60" s="2">
+        <v>17000000</v>
+      </c>
+      <c r="F60" s="2">
+        <v>17000000</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -18221,14 +18784,17 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D61" s="2">
+        <v>22500000</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -18236,14 +18802,23 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D62" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F62" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -18251,44 +18826,65 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>287</v>
+        <v>114</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D63" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="F63" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H63" s="2">
+        <v>15000000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64">
-        <v>305</v>
+        <v>157</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D64" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="F64" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H64" s="2">
+        <v>19000000</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D65" s="2">
+        <v>10000000</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -18296,14 +18892,14 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -18311,14 +18907,29 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>49</v>
+        <v>262</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="F67" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H67" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Derik Queen</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -18326,14 +18937,14 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -18341,14 +18952,20 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>220</v>
+        <v>143</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D69" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="F69" s="2">
+        <v>21000000</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -18356,14 +18973,14 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -18371,14 +18988,29 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2800000</v>
+      </c>
+      <c r="F71" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H71" s="2">
+        <v>3300000</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Collin Murray-Boyles</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -18386,14 +19018,20 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D72" s="2">
+        <v>17000000</v>
+      </c>
+      <c r="F72" s="2">
+        <v>17000000</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>VJ Edgecombe</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -18401,14 +19039,23 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>219</v>
+        <v>17</v>
       </c>
       <c r="C73">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D73" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F73" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H73" s="2">
+        <v>40000000</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -18416,14 +19063,20 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C74">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D74" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F74" s="2">
+        <v>3100000</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -18431,59 +19084,59 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C75">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B76">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B77">
-        <v>338</v>
+        <v>148</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B78">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -18491,14 +19144,20 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F79" s="2">
+        <v>6000000</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -18506,14 +19165,17 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>98</v>
+        <v>338</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D80" s="2">
+        <v>1000000</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -18521,14 +19183,14 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -18536,14 +19198,14 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -18551,14 +19213,14 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -18566,14 +19228,14 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -18581,14 +19243,17 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D85" s="2">
+        <v>20000000</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -18596,14 +19261,14 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -18611,104 +19276,128 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="C87">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="D87" s="2">
+        <v>7000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B88">
-        <v>242</v>
+        <v>97</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D88" s="2">
+        <v>35000000</v>
+      </c>
+      <c r="F88" s="2">
+        <v>35000000</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B89">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="D89" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F89" s="2">
+        <v>3100000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B90">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="D90" s="2">
+        <v>1000000</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B91">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B92">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="D92" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F92" s="2">
+        <v>6000000</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C93">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -18716,14 +19405,23 @@
         <v>8</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>242</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="F94" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -18731,14 +19429,14 @@
         <v>8</v>
       </c>
       <c r="B95">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -18746,14 +19444,29 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C96">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="D96" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H96" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -18761,14 +19474,17 @@
         <v>8</v>
       </c>
       <c r="B97">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C97">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="D97" s="2">
+        <v>2000000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -18776,14 +19492,23 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>203</v>
+        <v>116</v>
       </c>
       <c r="C98">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="D98" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F98" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H98" s="2">
+        <v>6000000</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -18791,134 +19516,176 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>225</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="D99" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="F99" s="2">
+        <v>7500000</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B100">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D100" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="F100" s="2">
+        <v>4000000</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B101">
-        <v>240</v>
+        <v>14</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="D101" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F101" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H101" s="2">
+        <v>16000000</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
+        <v>8</v>
+      </c>
+      <c r="B102">
+        <v>83</v>
+      </c>
+      <c r="C102">
         <v>9</v>
       </c>
-      <c r="B102">
-        <v>186</v>
-      </c>
-      <c r="C102">
-        <v>3</v>
+      <c r="D102" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="F102" s="2">
+        <v>9000000</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B103">
-        <v>251</v>
+        <v>84</v>
       </c>
       <c r="C103">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="D103" s="2">
+        <v>16000000</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B104">
-        <v>273</v>
+        <v>203</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="D104" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="F104" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H104" s="2">
+        <v>19000000</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B105">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Ousmane Dieng</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B106">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B107">
-        <v>26</v>
+        <v>336</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -18926,14 +19693,23 @@
         <v>9</v>
       </c>
       <c r="B108">
-        <v>89</v>
+        <v>384</v>
       </c>
       <c r="C108">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="D108" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F108" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H108" s="2">
+        <v>3100000</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -18941,14 +19717,14 @@
         <v>9</v>
       </c>
       <c r="B109">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="C109">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -18956,14 +19732,17 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="C110">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D110" s="2">
+        <v>4500000</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -18971,808 +19750,1252 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>331</v>
+        <v>251</v>
       </c>
       <c r="C111">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B112">
-        <v>303</v>
+        <v>416</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Scoot Henderson</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113">
-        <v>373</v>
+        <v>170</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D113" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F113" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H113" s="2">
+        <v>3100000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B114">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="D114" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="F114" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="H114" s="2">
+        <v>32000000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B115">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="C115">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="D115" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="F115" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="H115" s="2">
+        <v>12500000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B116">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="D116" s="2">
+        <v>11500000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
+        <v>9</v>
+      </c>
+      <c r="B117">
+        <v>167</v>
+      </c>
+      <c r="C117">
         <v>10</v>
       </c>
-      <c r="B117">
-        <v>168</v>
-      </c>
-      <c r="C117">
-        <v>6</v>
+      <c r="D117" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F117" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H117" s="2">
+        <v>3100000</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
+        <v>9</v>
+      </c>
+      <c r="B118">
+        <v>217</v>
+      </c>
+      <c r="C118">
         <v>11</v>
       </c>
-      <c r="B118">
-        <v>327</v>
-      </c>
-      <c r="C118">
-        <v>1</v>
+      <c r="D118" s="2">
+        <v>25000000</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B119">
-        <v>213</v>
+        <v>331</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D119" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F119" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H119" s="2">
+        <v>12000000</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B120">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="C120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B121">
-        <v>58</v>
+        <v>373</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B122">
-        <v>18</v>
+        <v>249</v>
       </c>
       <c r="C122">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B123">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="C123">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D123" s="2">
+        <v>4100000</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B124">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="D124" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F124" s="2">
+        <v>6000000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B125">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C125">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1000000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B126">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C126">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B127">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="C127">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D127" s="2">
+        <v>9250000</v>
+      </c>
+      <c r="F127" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B128">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="C128">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D128" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="F128" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H128" s="2">
+        <v>15000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B129">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="C129">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="D129" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="F129" s="2">
+        <v>11000000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B130">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D130" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F130" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H130" s="2">
+        <v>16000000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Cody Williams</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
+        <v>10</v>
+      </c>
+      <c r="B131">
+        <v>246</v>
+      </c>
+      <c r="C131">
         <v>12</v>
       </c>
-      <c r="B131">
-        <v>345</v>
-      </c>
-      <c r="C131">
-        <v>2</v>
+      <c r="D131" s="2">
+        <v>24000000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B132">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Yves Missi</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B133">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B134">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D134" s="2">
+        <v>1000000</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Goga Bitadze</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B135">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="C135">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Micah Potter</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B136">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="D136" s="2">
+        <v>1000000</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B137">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C137">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B138">
-        <v>194</v>
+        <v>6</v>
       </c>
       <c r="C138">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D138" s="2">
+        <v>26000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B139">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D139" s="2">
+        <v>15000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B140">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="C140">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D140" s="2">
+        <v>7500000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B141">
-        <v>307</v>
+        <v>166</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D141" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="F141" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="H141" s="2">
+        <v>30000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B142">
-        <v>363</v>
+        <v>248</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="D142" s="2">
+        <v>1000000</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B143">
-        <v>296</v>
+        <v>109</v>
       </c>
       <c r="C143">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
+        <v>11</v>
+      </c>
+      <c r="B144">
+        <v>266</v>
+      </c>
+      <c r="C144">
         <v>13</v>
-      </c>
-      <c r="B144">
-        <v>171</v>
-      </c>
-      <c r="C144">
-        <v>4</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B145">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B146">
-        <v>46</v>
+        <v>403</v>
       </c>
       <c r="C146">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F146" s="2">
+        <v>5000000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B147">
-        <v>4</v>
+        <v>345</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="D147" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="F147" s="2">
+        <v>3500000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B148">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="C148">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="D148" s="2">
+        <v>1000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B149">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C149">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B150">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D150" s="2">
+        <v>11000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B151">
-        <v>94</v>
+        <v>194</v>
       </c>
       <c r="C151">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D151" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F151" s="2">
+        <v>20000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Zach Collins</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B152">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="C152">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="D152" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="F152" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="H152" s="2">
+        <v>18000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B153">
-        <v>317</v>
+        <v>115</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D153" s="2">
+        <v>2500000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B154">
-        <v>241</v>
+        <v>307</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D154" s="2">
+        <v>1000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B155">
-        <v>129</v>
+        <v>363</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B156">
-        <v>93</v>
+        <v>296</v>
       </c>
       <c r="C156">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D156" s="2">
+        <v>3000000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B157">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="C157">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D157" s="2">
+        <v>2000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B158">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Toumani Camara</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B159">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C159">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B160">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="C160">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D160" s="2">
+        <v>11500000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B161">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C161">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D161" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F161" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H161" s="2">
+        <v>16000000</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B162">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="C162">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D162" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F162" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H162" s="2">
+        <v>12000000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B163">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="C163">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="D163" s="2">
+        <v>19000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B164">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="C164">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D164" s="2">
+        <v>1000000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
+        <v>Zach Collins</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>13</v>
+      </c>
+      <c r="B165">
+        <v>150</v>
+      </c>
+      <c r="C165">
+        <v>12</v>
+      </c>
+      <c r="D165" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F165" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H165" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="L165" t="str">
+        <f>VLOOKUP(B165,players!A:B,2)</f>
+        <v>Austin Reaves</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>14</v>
+      </c>
+      <c r="B166">
+        <v>317</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="L166" t="str">
+        <f>VLOOKUP(B166,players!A:B,2)</f>
+        <v>Anfernee Simons</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>14</v>
+      </c>
+      <c r="B167">
+        <v>299</v>
+      </c>
+      <c r="C167">
+        <v>2</v>
+      </c>
+      <c r="L167" t="str">
+        <f>VLOOKUP(B167,players!A:B,2)</f>
+        <v>Marcus Smart</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>14</v>
+      </c>
+      <c r="B168">
+        <v>129</v>
+      </c>
+      <c r="C168">
+        <v>3</v>
+      </c>
+      <c r="L168" t="str">
+        <f>VLOOKUP(B168,players!A:B,2)</f>
+        <v>Jaime Jaquez Jr.</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>14</v>
+      </c>
+      <c r="B169">
+        <v>90</v>
+      </c>
+      <c r="C169">
+        <v>4</v>
+      </c>
+      <c r="L169" t="str">
+        <f>VLOOKUP(B169,players!A:B,2)</f>
+        <v>Jimmy Butler</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>14</v>
+      </c>
+      <c r="B170">
+        <v>24</v>
+      </c>
+      <c r="C170">
+        <v>5</v>
+      </c>
+      <c r="D170" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="L170" t="str">
+        <f>VLOOKUP(B170,players!A:B,2)</f>
+        <v>Moussa Diabaté</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>14</v>
+      </c>
+      <c r="B171">
+        <v>238</v>
+      </c>
+      <c r="C171">
+        <v>6</v>
+      </c>
+      <c r="D171" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="L171" t="str">
+        <f>VLOOKUP(B171,players!A:B,2)</f>
+        <v>Coby White</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>14</v>
+      </c>
+      <c r="B172">
+        <v>19</v>
+      </c>
+      <c r="C172">
+        <v>7</v>
+      </c>
+      <c r="D172" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="F172" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="H172" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="L172" t="str">
+        <f>VLOOKUP(B172,players!A:B,2)</f>
+        <v>Evan Mobley</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>14</v>
+      </c>
+      <c r="B173">
+        <v>73</v>
+      </c>
+      <c r="C173">
+        <v>8</v>
+      </c>
+      <c r="D173" s="2">
+        <v>19500000</v>
+      </c>
+      <c r="L173" t="str">
+        <f>VLOOKUP(B173,players!A:B,2)</f>
+        <v>LeBron James</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>14</v>
+      </c>
+      <c r="B174">
+        <v>61</v>
+      </c>
+      <c r="C174">
+        <v>9</v>
+      </c>
+      <c r="D174" s="2">
+        <v>9500000</v>
+      </c>
+      <c r="F174" s="2">
+        <v>10500000</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H174" s="2">
+        <v>11500000</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L174" t="str">
+        <f>VLOOKUP(B174,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>14</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+      <c r="C175">
+        <v>10</v>
+      </c>
+      <c r="L175" t="str">
+        <f>VLOOKUP(B175,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>14</v>
+      </c>
+      <c r="B176">
+        <v>220</v>
+      </c>
+      <c r="C176">
+        <v>11</v>
+      </c>
+      <c r="L176" t="str">
+        <f>VLOOKUP(B176,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>14</v>
+      </c>
+      <c r="B177">
+        <v>145</v>
+      </c>
+      <c r="C177">
+        <v>12</v>
+      </c>
+      <c r="D177" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F177" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H177" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="L177" t="str">
+        <f>VLOOKUP(B177,players!A:B,2)</f>
         <v>LaMelo Ball</v>
       </c>
     </row>
@@ -19784,7 +21007,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B357A823-6505-4984-ACC9-40636E218B6C}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
@@ -19792,6 +21015,7 @@
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -19828,6 +21052,9 @@
       <c r="K1" t="s">
         <v>460</v>
       </c>
+      <c r="L1" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -19853,7 +21080,10 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="L2" t="str">
+        <f>VLOOKUP(B2,players!A:B,2)</f>
+        <v>Rob Dillingham</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -19879,7 +21109,10 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="L3" t="str">
+        <f>VLOOKUP(B3,players!A:B,2)</f>
+        <v>Tristan Da Silva</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -19905,7 +21138,10 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="L4" t="str">
+        <f>VLOOKUP(B4,players!A:B,2)</f>
+        <v>Isaiah Collier</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -19935,7 +21171,10 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="L5" t="str">
+        <f>VLOOKUP(B5,players!A:B,2)</f>
+        <v>Ryan Kalkbrenner</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -19948,58 +21187,70 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>8250000</v>
+        <v>4500000</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2">
-        <v>4500000</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>5000000</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H6" s="2">
-        <v>5000000</v>
+        <v>5500000</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="J6" s="2">
-        <v>5500000</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="L6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" t="str">
+        <f>VLOOKUP(B6,players!A:B,2)</f>
+        <v>Jeremiah Fears</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>3900000</v>
+        <v>1000000</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="F7" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="L7" t="str">
+        <f>VLOOKUP(B7,players!A:B,2)</f>
+        <v>Walter Clayton</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
       <c r="B8">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2">
         <v>1000000</v>
@@ -20011,25 +21262,24 @@
       <c r="G8" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H8" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="L8" t="str">
+        <f>VLOOKUP(B8,players!A:B,2)</f>
+        <v>Johnny Furphy</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2">
         <v>1000000</v>
@@ -20041,107 +21291,123 @@
       <c r="G9" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="H9" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="L9" t="str">
+        <f>VLOOKUP(B9,players!A:B,2)</f>
+        <v>Nikola Topić</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>1000000</v>
+        <v>3400000</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
-        <v>1000000</v>
+        <v>3700000</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H10" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" t="str">
+        <f>VLOOKUP(B10,players!A:B,2)</f>
+        <v>Jase Richardson</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>408</v>
+        <v>92</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>3400000</v>
+        <v>6500000</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2">
-        <v>3700000</v>
+        <v>7000000</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="H11" s="2">
+        <v>7500000</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" t="str">
+        <f>VLOOKUP(B11,players!A:B,2)</f>
+        <v>VJ Edgecombe</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12">
-        <v>305</v>
+        <v>139</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H12" s="2">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>472</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" t="str">
+        <f>VLOOKUP(B12,players!A:B,2)</f>
+        <v>Danny Wolf</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
         <v>1000000</v>
@@ -20161,84 +21427,89 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="L13" t="str">
+        <f>VLOOKUP(B13,players!A:B,2)</f>
+        <v>Nique Clifford</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14">
-        <v>274</v>
+        <v>409</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2">
-        <v>1000000</v>
+        <v>4200000</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H14" s="2">
-        <v>1000000</v>
+        <v>4500000</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>472</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="L14" t="str">
+        <f>VLOOKUP(B14,players!A:B,2)</f>
+        <v>Hansen Yang</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15">
-        <v>409</v>
+        <v>192</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>4000000</v>
+        <v>3200000</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2">
-        <v>4200000</v>
+        <v>3500000</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H15" s="2">
-        <v>4500000</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="L15" t="str">
+        <f>VLOOKUP(B15,players!A:B,2)</f>
+        <v>Tidjane Salaün</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B16">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2">
-        <v>3500000</v>
+        <v>1000000</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>472</v>
@@ -20247,73 +21518,82 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="L16" t="str">
+        <f>VLOOKUP(B16,players!A:B,2)</f>
+        <v>Kyle Filipowski</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="H17" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="L17" t="str">
+        <f>VLOOKUP(B17,players!A:B,2)</f>
+        <v>Kon Knueppel</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9</v>
       </c>
       <c r="B18">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H18" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="L18" t="str">
+        <f>VLOOKUP(B18,players!A:B,2)</f>
+        <v>Jaylon Tyson</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9</v>
       </c>
       <c r="B19">
-        <v>123</v>
+        <v>410</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
         <v>1000000</v>
@@ -20329,178 +21609,195 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="L19" t="str">
+        <f>VLOOKUP(B19,players!A:B,2)</f>
+        <v>Joan Beringer</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
-        <v>410</v>
+        <v>297</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="H20" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+      <c r="L20" t="str">
+        <f>VLOOKUP(B20,players!A:B,2)</f>
+        <v>Tre Johnson</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>10</v>
       </c>
       <c r="B21">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H21" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>472</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="L21" t="str">
+        <f>VLOOKUP(B21,players!A:B,2)</f>
+        <v>Ja'Kobe Walter</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>10</v>
       </c>
       <c r="B22">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2">
-        <v>1000000</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="L22" t="str">
+        <f>VLOOKUP(B22,players!A:B,2)</f>
+        <v>Cam Whitmore</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>10</v>
       </c>
       <c r="B23">
-        <v>300</v>
+        <v>411</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="F23" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="L23" t="str">
+        <f>VLOOKUP(B23,players!A:B,2)</f>
+        <v>Thomas Sorber</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2">
-        <v>1000000</v>
+        <v>3500000</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H24" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="L24" t="str">
+        <f>VLOOKUP(B24,players!A:B,2)</f>
+        <v>Carter Bryant</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>11</v>
       </c>
       <c r="B25">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2">
-        <v>3200000</v>
+        <v>3300000</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="L25" t="str">
+        <f>VLOOKUP(B25,players!A:B,2)</f>
+        <v>Dalton Knecht</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>11</v>
       </c>
       <c r="B26">
-        <v>413</v>
+        <v>189</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
-        <v>3300000</v>
+        <v>6000000</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -20509,191 +21806,190 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="L26" t="str">
+        <f>VLOOKUP(B26,players!A:B,2)</f>
+        <v>Ron Holland</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B27">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="F27" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="L27" t="str">
+        <f>VLOOKUP(B27,players!A:B,2)</f>
+        <v>Devin Carter</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13</v>
       </c>
       <c r="B28">
-        <v>252</v>
+        <v>414</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="H28" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
+      <c r="L28" t="str">
+        <f>VLOOKUP(B28,players!A:B,2)</f>
+        <v>Kaman Maluach</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13</v>
       </c>
       <c r="B29">
-        <v>414</v>
+        <v>241</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2">
-        <v>3600000</v>
+        <v>8500000</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2">
-        <v>3800000</v>
+        <v>9250000</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H29" s="2">
-        <v>4100000</v>
+        <v>10000000</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>472</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
+      <c r="L29" t="str">
+        <f>VLOOKUP(B29,players!A:B,2)</f>
+        <v>Dylan Harper</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B30">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2">
-        <v>8500000</v>
+        <v>3200000</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2">
-        <v>9250000</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H30" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>472</v>
-      </c>
+        <v>3500000</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
+      <c r="L30" t="str">
+        <f>VLOOKUP(B30,players!A:B,2)</f>
+        <v>Cason Wallace</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>14</v>
       </c>
       <c r="B31">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2">
-        <v>3200000</v>
+        <v>1000000</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2">
-        <v>3500000</v>
-      </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
+      <c r="L31" t="str">
+        <f>VLOOKUP(B31,players!A:B,2)</f>
+        <v>Jaylen Wells</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>14</v>
       </c>
       <c r="B32">
-        <v>259</v>
+        <v>415</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="F32" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4200000</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>14</v>
-      </c>
-      <c r="B33">
-        <v>415</v>
-      </c>
-      <c r="C33">
-        <v>3</v>
-      </c>
-      <c r="D33" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2">
-        <v>4000000</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H33" s="2">
-        <v>4200000</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+      <c r="L32" t="str">
+        <f>VLOOKUP(B32,players!A:B,2)</f>
+        <v>Noah Essengue</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Fantasy unificado/roster.xlsx
+++ b/Fantasy unificado/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62FFA30F-5A49-4041-9C0E-7735BFB4A2F2}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="13_ncr:1_{430BDD2D-160C-44D5-BB14-2292BAF4F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCB96EE-9DD3-443F-9441-041433179731}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3A1DF636-5ABD-4BA5-9760-0119E916B26D}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="635">
   <si>
     <t>player_id</t>
   </si>
@@ -1623,6 +1623,339 @@
   </si>
   <si>
     <t>SG/SF</t>
+  </si>
+  <si>
+    <t>P2026_R1_T09</t>
+  </si>
+  <si>
+    <t>P2026_R2_T07</t>
+  </si>
+  <si>
+    <t>P2028_R1_T07</t>
+  </si>
+  <si>
+    <t>P2028_R2_T07</t>
+  </si>
+  <si>
+    <t>P2029_R1_T07</t>
+  </si>
+  <si>
+    <t>P2029_R2_T07</t>
+  </si>
+  <si>
+    <t>P2026_R1_T01</t>
+  </si>
+  <si>
+    <t>P2026_R1_T11</t>
+  </si>
+  <si>
+    <t>P2026_R1_T02</t>
+  </si>
+  <si>
+    <t>P2026_R2_T01</t>
+  </si>
+  <si>
+    <t>P2026_R2_T05</t>
+  </si>
+  <si>
+    <t>P2027_R1_T01</t>
+  </si>
+  <si>
+    <t>P2027_R2_T01</t>
+  </si>
+  <si>
+    <t>P2027_R2_T05</t>
+  </si>
+  <si>
+    <t>P2027_R2_T06</t>
+  </si>
+  <si>
+    <t>P2028_R1_T01</t>
+  </si>
+  <si>
+    <t>P2028_R2_T01</t>
+  </si>
+  <si>
+    <t>P2029_R1_T01</t>
+  </si>
+  <si>
+    <t>P2029_R2_T01</t>
+  </si>
+  <si>
+    <t>P2026_R1_T10</t>
+  </si>
+  <si>
+    <t>P2026_R2_T02</t>
+  </si>
+  <si>
+    <t>P2027_R1_T02</t>
+  </si>
+  <si>
+    <t>P2028_R1_T02</t>
+  </si>
+  <si>
+    <t>P2029_R1_T02</t>
+  </si>
+  <si>
+    <t>P2028_R2_T02</t>
+  </si>
+  <si>
+    <t>P2029_R2_T02</t>
+  </si>
+  <si>
+    <t>P2026_R1_T03</t>
+  </si>
+  <si>
+    <t>P2027_R1_T03</t>
+  </si>
+  <si>
+    <t>P2027_R2_T03</t>
+  </si>
+  <si>
+    <t>P2028_R1_T03</t>
+  </si>
+  <si>
+    <t>P2028_R2_T03</t>
+  </si>
+  <si>
+    <t>P2029_R1_T03</t>
+  </si>
+  <si>
+    <t>P2029_R2_T03</t>
+  </si>
+  <si>
+    <t>P2026_R2_T04</t>
+  </si>
+  <si>
+    <t>P2027_R2_T04</t>
+  </si>
+  <si>
+    <t>P2027_R1_T04</t>
+  </si>
+  <si>
+    <t>P2028_R1_T04</t>
+  </si>
+  <si>
+    <t>P2028_R2_T04</t>
+  </si>
+  <si>
+    <t>P2029_R1_T04</t>
+  </si>
+  <si>
+    <t>P2029_R2_T04</t>
+  </si>
+  <si>
+    <t>P2026_R1_T14</t>
+  </si>
+  <si>
+    <t>P2026_R1_T13</t>
+  </si>
+  <si>
+    <t>P2026_R2_T14</t>
+  </si>
+  <si>
+    <t>P2026_R2_T10</t>
+  </si>
+  <si>
+    <t>P2026_R1_T05</t>
+  </si>
+  <si>
+    <t>P2027_R1_T05</t>
+  </si>
+  <si>
+    <t>P2027_R2_T07</t>
+  </si>
+  <si>
+    <t>P2028_R2_T05</t>
+  </si>
+  <si>
+    <t>P2029_R1_T05</t>
+  </si>
+  <si>
+    <t>P2029_R2_T05</t>
+  </si>
+  <si>
+    <t>P2026_R1_T06</t>
+  </si>
+  <si>
+    <t>P2026_R2_T06</t>
+  </si>
+  <si>
+    <t>P2027_R1_T06</t>
+  </si>
+  <si>
+    <t>P2028_R1_T06</t>
+  </si>
+  <si>
+    <t>P2029_R1_T06</t>
+  </si>
+  <si>
+    <t>P2028_R1_T05</t>
+  </si>
+  <si>
+    <t>P2029_R2_T06</t>
+  </si>
+  <si>
+    <t>P2026_R1_T08</t>
+  </si>
+  <si>
+    <t>P2026_R2_T08</t>
+  </si>
+  <si>
+    <t>P2026_R2_T03</t>
+  </si>
+  <si>
+    <t>P2027_R1_T08</t>
+  </si>
+  <si>
+    <t>P2027_R2_T08</t>
+  </si>
+  <si>
+    <t>P2028_R1_T08</t>
+  </si>
+  <si>
+    <t>P2028_R2_T08</t>
+  </si>
+  <si>
+    <t>P2028_R2_T06</t>
+  </si>
+  <si>
+    <t>P2029_R1_T08</t>
+  </si>
+  <si>
+    <t>P2029_R2_T08</t>
+  </si>
+  <si>
+    <t>P2026_R2_T09</t>
+  </si>
+  <si>
+    <t>P2027_R1_T09</t>
+  </si>
+  <si>
+    <t>P2027_R2_T09</t>
+  </si>
+  <si>
+    <t>P2028_R1_T09</t>
+  </si>
+  <si>
+    <t>P2028_R2_T09</t>
+  </si>
+  <si>
+    <t>P2029_R1_T09</t>
+  </si>
+  <si>
+    <t>P2029_R2_T09</t>
+  </si>
+  <si>
+    <t>P2026_R2_T13</t>
+  </si>
+  <si>
+    <t>P2027_R1_T10</t>
+  </si>
+  <si>
+    <t>P2028_R1_T10</t>
+  </si>
+  <si>
+    <t>P2029_R1_T10</t>
+  </si>
+  <si>
+    <t>P2029_R2_T10</t>
+  </si>
+  <si>
+    <t>P2028_R2_T10</t>
+  </si>
+  <si>
+    <t>P2027_R1_T07</t>
+  </si>
+  <si>
+    <t>P2027_R2_T10</t>
+  </si>
+  <si>
+    <t>P2026_R2_T11</t>
+  </si>
+  <si>
+    <t>P2029_R2_T11</t>
+  </si>
+  <si>
+    <t>P2028_R2_T11</t>
+  </si>
+  <si>
+    <t>P2027_R2_T11</t>
+  </si>
+  <si>
+    <t>P2027_R1_T11</t>
+  </si>
+  <si>
+    <t>P2028_R1_T11</t>
+  </si>
+  <si>
+    <t>P2029_R1_T11</t>
+  </si>
+  <si>
+    <t>P2026_R1_T12</t>
+  </si>
+  <si>
+    <t>P2026_R2_T12</t>
+  </si>
+  <si>
+    <t>P2027_R1_T12</t>
+  </si>
+  <si>
+    <t>P2027_R2_T12</t>
+  </si>
+  <si>
+    <t>P2028_R1_T12</t>
+  </si>
+  <si>
+    <t>P2028_R2_T12</t>
+  </si>
+  <si>
+    <t>P2029_R1_T12</t>
+  </si>
+  <si>
+    <t>P2029_R2_T12</t>
+  </si>
+  <si>
+    <t>P2026_R1_T04</t>
+  </si>
+  <si>
+    <t>P2027_R1_T13</t>
+  </si>
+  <si>
+    <t>P2027_R2_T13</t>
+  </si>
+  <si>
+    <t>P2028_R1_T13</t>
+  </si>
+  <si>
+    <t>P2028_R2_T13</t>
+  </si>
+  <si>
+    <t>P2029_R1_T13</t>
+  </si>
+  <si>
+    <t>P2029_R2_T13</t>
+  </si>
+  <si>
+    <t>P2027_R1_T14</t>
+  </si>
+  <si>
+    <t>P2027_R2_T14</t>
+  </si>
+  <si>
+    <t>P2027_R2_T02</t>
+  </si>
+  <si>
+    <t>P2028_R1_T14</t>
+  </si>
+  <si>
+    <t>P2028_R2_T14</t>
+  </si>
+  <si>
+    <t>P2029_R1_T14</t>
+  </si>
+  <si>
+    <t>P2029_R2_T14</t>
   </si>
 </sst>
 </file>
@@ -17539,7 +17872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E67E5-331D-4CC3-B636-B44F8A41C81C}">
-  <dimension ref="A1:L177"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -18295,104 +18628,74 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2">
-        <v>3200000</v>
+        <v>3100000</v>
       </c>
       <c r="F37" s="2">
-        <v>3400000</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>472</v>
+        <v>3100000</v>
       </c>
       <c r="H37" s="2">
-        <v>3700000</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>472</v>
+        <v>3100000</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Derik Queen</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2">
-        <v>3100000</v>
+        <v>8000000</v>
       </c>
       <c r="F38" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H38" s="2">
-        <v>3100000</v>
+        <v>8000000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>237</v>
+      </c>
+      <c r="C39">
         <v>2</v>
-      </c>
-      <c r="B39">
-        <v>8</v>
-      </c>
-      <c r="C39">
-        <v>11</v>
-      </c>
-      <c r="D39" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F39" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Zach Edey</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B40">
-        <v>290</v>
+        <v>119</v>
       </c>
       <c r="C40">
-        <v>12</v>
-      </c>
-      <c r="D40" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H40" s="2">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Will Riley</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -18400,20 +18703,17 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" s="2">
-        <v>8000000</v>
-      </c>
-      <c r="F41" s="2">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -18421,14 +18721,14 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -18436,14 +18736,14 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -18451,17 +18751,14 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>206</v>
+        <v>11</v>
       </c>
       <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2">
-        <v>5000000</v>
+        <v>7</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -18469,14 +18766,23 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D45" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F45" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H45" s="2">
+        <v>40000000</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -18484,14 +18790,17 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D46" s="2">
+        <v>6000000</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -18499,14 +18808,20 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D47" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="F47" s="2">
+        <v>14000000</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -18514,23 +18829,23 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2">
-        <v>40000000</v>
+        <v>6500000</v>
       </c>
       <c r="F48" s="2">
-        <v>40000000</v>
+        <v>6500000</v>
       </c>
       <c r="H48" s="2">
-        <v>40000000</v>
+        <v>6500000</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -18538,17 +18853,17 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D49" s="2">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -18556,80 +18871,86 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2">
-        <v>14000000</v>
-      </c>
-      <c r="F50" s="2">
-        <v>14000000</v>
+        <v>8000000</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B51">
-        <v>117</v>
+        <v>379</v>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="F51" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="H51" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B52">
-        <v>142</v>
+        <v>364</v>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2">
-        <v>5000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>104</v>
+      </c>
+      <c r="C53">
         <v>3</v>
-      </c>
-      <c r="B53">
-        <v>295</v>
-      </c>
-      <c r="C53">
-        <v>13</v>
-      </c>
-      <c r="D53" s="2">
-        <v>8000000</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -18637,29 +18958,17 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>379</v>
+        <v>62</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F54" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H54" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>472</v>
+        <v>2500000</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -18667,23 +18976,17 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>364</v>
+        <v>33</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="F55" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>472</v>
+        <v>11000000</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -18691,14 +18994,20 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D56" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F56" s="2">
+        <v>5000000</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -18706,17 +19015,20 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D57" s="2">
-        <v>2500000</v>
+        <v>17000000</v>
+      </c>
+      <c r="F57" s="2">
+        <v>17000000</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -18724,17 +19036,17 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2">
-        <v>11000000</v>
+        <v>22500000</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -18742,20 +19054,23 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2">
         <v>5000000</v>
       </c>
       <c r="F59" s="2">
-        <v>5000000</v>
+        <v>5500000</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -18763,20 +19078,23 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D60" s="2">
-        <v>17000000</v>
+        <v>15000000</v>
       </c>
       <c r="F60" s="2">
-        <v>17000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="H60" s="2">
+        <v>15000000</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -18784,17 +19102,23 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2">
-        <v>22500000</v>
+        <v>19000000</v>
+      </c>
+      <c r="F61" s="2">
+        <v>19000000</v>
+      </c>
+      <c r="H61" s="2">
+        <v>19000000</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -18802,89 +19126,77 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>110</v>
+        <v>287</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="F62" s="2">
-        <v>5500000</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>472</v>
+        <v>10000000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B63">
-        <v>114</v>
+        <v>305</v>
       </c>
       <c r="C63">
-        <v>10</v>
-      </c>
-      <c r="D63" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="F63" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="H63" s="2">
-        <v>15000000</v>
+        <v>1</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B64">
-        <v>157</v>
+        <v>262</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2">
-        <v>19000000</v>
+        <v>3600000</v>
       </c>
       <c r="F64" s="2">
-        <v>19000000</v>
+        <v>3800000</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="H64" s="2">
-        <v>19000000</v>
+        <v>4100000</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B65">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C65">
-        <v>12</v>
-      </c>
-      <c r="D65" s="2">
-        <v>10000000</v>
+        <v>3</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -18892,14 +19204,20 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>305</v>
+        <v>143</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D66" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="F66" s="2">
+        <v>21000000</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -18907,29 +19225,14 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>262</v>
+        <v>131</v>
       </c>
       <c r="C67">
-        <v>2</v>
-      </c>
-      <c r="D67" s="2">
-        <v>3600000</v>
-      </c>
-      <c r="F67" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H67" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>472</v>
+        <v>5</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -18937,14 +19240,29 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>274</v>
+        <v>139</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D68" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F68" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -18952,20 +19270,20 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D69" s="2">
-        <v>21000000</v>
+        <v>17000000</v>
       </c>
       <c r="F69" s="2">
-        <v>21000000</v>
+        <v>17000000</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -18973,14 +19291,23 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D70" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="F70" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="H70" s="2">
+        <v>40000000</v>
       </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -18988,29 +19315,20 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2">
-        <v>2800000</v>
+        <v>3100000</v>
       </c>
       <c r="F71" s="2">
-        <v>3000000</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H71" s="2">
-        <v>3300000</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>472</v>
+        <v>3100000</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Collin Murray-Boyles</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -19018,20 +19336,14 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>37</v>
+        <v>227</v>
       </c>
       <c r="C72">
-        <v>7</v>
-      </c>
-      <c r="D72" s="2">
-        <v>17000000</v>
-      </c>
-      <c r="F72" s="2">
-        <v>17000000</v>
+        <v>10</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -19039,23 +19351,14 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C73">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="F73" s="2">
-        <v>40000000</v>
-      </c>
-      <c r="H73" s="2">
-        <v>40000000</v>
+        <v>11</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -19063,20 +19366,14 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="C74">
-        <v>9</v>
-      </c>
-      <c r="D74" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F74" s="2">
-        <v>3100000</v>
+        <v>12</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -19084,59 +19381,68 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B76">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="C76">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="D76" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F76" s="2">
+        <v>6000000</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B77">
-        <v>148</v>
+        <v>338</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="D77" s="2">
+        <v>1000000</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="C78">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -19144,20 +19450,14 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F79" s="2">
-        <v>6000000</v>
+        <v>4</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -19165,17 +19465,14 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>338</v>
+        <v>98</v>
       </c>
       <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80" s="2">
-        <v>1000000</v>
+        <v>5</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -19183,14 +19480,14 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -19198,14 +19495,17 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D82" s="2">
+        <v>20000000</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -19213,14 +19513,14 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -19228,14 +19528,17 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="C84">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D84" s="2">
+        <v>7000000</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -19243,17 +19546,20 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D85" s="2">
-        <v>20000000</v>
+        <v>35000000</v>
+      </c>
+      <c r="F85" s="2">
+        <v>35000000</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -19261,14 +19567,20 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="D86" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F86" s="2">
+        <v>3100000</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -19276,17 +19588,17 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="C87">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D87" s="2">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -19294,20 +19606,14 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="C88">
-        <v>10</v>
-      </c>
-      <c r="D88" s="2">
-        <v>35000000</v>
-      </c>
-      <c r="F88" s="2">
-        <v>35000000</v>
+        <v>13</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -19315,20 +19621,20 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C89">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D89" s="2">
-        <v>3100000</v>
+        <v>6000000</v>
       </c>
       <c r="F89" s="2">
-        <v>3100000</v>
+        <v>6000000</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -19336,68 +19642,83 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="C90">
-        <v>12</v>
-      </c>
-      <c r="D90" s="2">
-        <v>1000000</v>
+        <v>15</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B91">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="C91">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="F91" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B92">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="C92">
-        <v>14</v>
-      </c>
-      <c r="D92" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F92" s="2">
-        <v>6000000</v>
+        <v>2</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B93">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C93">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H93" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -19405,23 +19726,17 @@
         <v>8</v>
       </c>
       <c r="B94">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D94" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="F94" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>472</v>
+        <v>2000000</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -19429,14 +19744,23 @@
         <v>8</v>
       </c>
       <c r="B95">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D95" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F95" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H95" s="2">
+        <v>6000000</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -19444,29 +19768,23 @@
         <v>8</v>
       </c>
       <c r="B96">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D96" s="2">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="F96" s="2">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H96" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -19474,17 +19792,20 @@
         <v>8</v>
       </c>
       <c r="B97">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D97" s="2">
-        <v>2000000</v>
+        <v>4000000</v>
+      </c>
+      <c r="F97" s="2">
+        <v>4000000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -19492,23 +19813,23 @@
         <v>8</v>
       </c>
       <c r="B98">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D98" s="2">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="F98" s="2">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="H98" s="2">
-        <v>6000000</v>
+        <v>16000000</v>
       </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -19516,23 +19837,20 @@
         <v>8</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C99">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
       <c r="F99" s="2">
-        <v>7500000</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>472</v>
+        <v>9000000</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -19540,20 +19858,17 @@
         <v>8</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D100" s="2">
-        <v>4000000</v>
-      </c>
-      <c r="F100" s="2">
-        <v>4000000</v>
+        <v>16000000</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -19561,23 +19876,23 @@
         <v>8</v>
       </c>
       <c r="B101">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="C101">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D101" s="2">
-        <v>16000000</v>
+        <v>19000000</v>
       </c>
       <c r="F101" s="2">
-        <v>16000000</v>
+        <v>19000000</v>
       </c>
       <c r="H101" s="2">
-        <v>16000000</v>
+        <v>19000000</v>
       </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -19585,20 +19900,14 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="C102">
-        <v>9</v>
-      </c>
-      <c r="D102" s="2">
-        <v>9000000</v>
-      </c>
-      <c r="F102" s="2">
-        <v>9000000</v>
+        <v>12</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -19606,17 +19915,14 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="C103">
-        <v>10</v>
-      </c>
-      <c r="D103" s="2">
-        <v>16000000</v>
+        <v>13</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -19624,68 +19930,71 @@
         <v>8</v>
       </c>
       <c r="B104">
-        <v>203</v>
+        <v>336</v>
       </c>
       <c r="C104">
-        <v>11</v>
-      </c>
-      <c r="D104" s="2">
-        <v>19000000</v>
-      </c>
-      <c r="F104" s="2">
-        <v>19000000</v>
-      </c>
-      <c r="H104" s="2">
-        <v>19000000</v>
+        <v>14</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B105">
-        <v>225</v>
+        <v>384</v>
       </c>
       <c r="C105">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="D105" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="F105" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H105" s="2">
+        <v>3100000</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B106">
-        <v>59</v>
+        <v>240</v>
       </c>
       <c r="C106">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B107">
-        <v>336</v>
+        <v>186</v>
       </c>
       <c r="C107">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="D107" s="2">
+        <v>4500000</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -19693,23 +20002,14 @@
         <v>9</v>
       </c>
       <c r="B108">
-        <v>384</v>
+        <v>251</v>
       </c>
       <c r="C108">
-        <v>1</v>
-      </c>
-      <c r="D108" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F108" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H108" s="2">
-        <v>3100000</v>
+        <v>4</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -19717,14 +20017,14 @@
         <v>9</v>
       </c>
       <c r="B109">
-        <v>240</v>
+        <v>416</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -19732,17 +20032,23 @@
         <v>9</v>
       </c>
       <c r="B110">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D110" s="2">
-        <v>4500000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F110" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="H110" s="2">
+        <v>3100000</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -19750,14 +20056,23 @@
         <v>9</v>
       </c>
       <c r="B111">
-        <v>251</v>
+        <v>15</v>
       </c>
       <c r="C111">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D111" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="F111" s="2">
+        <v>32000000</v>
+      </c>
+      <c r="H111" s="2">
+        <v>32000000</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -19765,14 +20080,23 @@
         <v>9</v>
       </c>
       <c r="B112">
-        <v>416</v>
+        <v>26</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D112" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="F112" s="2">
+        <v>12500000</v>
+      </c>
+      <c r="H112" s="2">
+        <v>12500000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -19780,23 +20104,17 @@
         <v>9</v>
       </c>
       <c r="B113">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="C113">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F113" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H113" s="2">
-        <v>3100000</v>
+        <v>11500000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -19804,23 +20122,23 @@
         <v>9</v>
       </c>
       <c r="B114">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D114" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="F114" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="H114" s="2">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -19828,23 +20146,17 @@
         <v>9</v>
       </c>
       <c r="B115">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="C115">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D115" s="2">
-        <v>12500000</v>
-      </c>
-      <c r="F115" s="2">
-        <v>12500000</v>
-      </c>
-      <c r="H115" s="2">
-        <v>12500000</v>
+        <v>25000000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -19852,83 +20164,68 @@
         <v>9</v>
       </c>
       <c r="B116">
-        <v>89</v>
+        <v>331</v>
       </c>
       <c r="C116">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D116" s="2">
-        <v>11500000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F116" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H116" s="2">
+        <v>12000000</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
+        <v>10</v>
+      </c>
+      <c r="B117">
         <v>9</v>
       </c>
-      <c r="B117">
-        <v>167</v>
-      </c>
       <c r="C117">
-        <v>10</v>
-      </c>
-      <c r="D117" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="F117" s="2">
-        <v>3100000</v>
-      </c>
-      <c r="H117" s="2">
-        <v>3100000</v>
+        <v>1</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B118">
-        <v>217</v>
+        <v>373</v>
       </c>
       <c r="C118">
-        <v>11</v>
-      </c>
-      <c r="D118" s="2">
-        <v>25000000</v>
+        <v>2</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B119">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="C119">
-        <v>12</v>
-      </c>
-      <c r="D119" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="F119" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="H119" s="2">
-        <v>12000000</v>
+        <v>3</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -19936,14 +20233,17 @@
         <v>10</v>
       </c>
       <c r="B120">
-        <v>9</v>
+        <v>169</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D120" s="2">
+        <v>4100000</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -19951,14 +20251,20 @@
         <v>10</v>
       </c>
       <c r="B121">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D121" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="F121" s="2">
+        <v>6000000</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -19966,14 +20272,17 @@
         <v>10</v>
       </c>
       <c r="B122">
-        <v>249</v>
+        <v>168</v>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D122" s="2">
+        <v>1000000</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -19981,17 +20290,14 @@
         <v>10</v>
       </c>
       <c r="B123">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C123">
-        <v>4</v>
-      </c>
-      <c r="D123" s="2">
-        <v>4100000</v>
+        <v>7</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -19999,20 +20305,23 @@
         <v>10</v>
       </c>
       <c r="B124">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C124">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D124" s="2">
-        <v>6000000</v>
+        <v>9250000</v>
       </c>
       <c r="F124" s="2">
-        <v>6000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -20020,17 +20329,23 @@
         <v>10</v>
       </c>
       <c r="B125">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="C125">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2">
-        <v>1000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="F125" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H125" s="2">
+        <v>15000000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -20038,14 +20353,20 @@
         <v>10</v>
       </c>
       <c r="B126">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D126" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="F126" s="2">
+        <v>11000000</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -20053,23 +20374,23 @@
         <v>10</v>
       </c>
       <c r="B127">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D127" s="2">
-        <v>9250000</v>
+        <v>16000000</v>
       </c>
       <c r="F127" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>472</v>
+        <v>16000000</v>
+      </c>
+      <c r="H127" s="2">
+        <v>16000000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -20077,86 +20398,65 @@
         <v>10</v>
       </c>
       <c r="B128">
-        <v>60</v>
+        <v>246</v>
       </c>
       <c r="C128">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D128" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="F128" s="2">
-        <v>15000000</v>
-      </c>
-      <c r="H128" s="2">
-        <v>15000000</v>
+        <v>24000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B129">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="C129">
-        <v>10</v>
-      </c>
-      <c r="D129" s="2">
-        <v>11000000</v>
-      </c>
-      <c r="F129" s="2">
-        <v>11000000</v>
+        <v>1</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B130">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="C130">
-        <v>11</v>
-      </c>
-      <c r="D130" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="F130" s="2">
-        <v>16000000</v>
-      </c>
-      <c r="H130" s="2">
-        <v>16000000</v>
+        <v>2</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B131">
-        <v>246</v>
+        <v>111</v>
       </c>
       <c r="C131">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D131" s="2">
-        <v>24000000</v>
+        <v>1000000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -20164,14 +20464,14 @@
         <v>11</v>
       </c>
       <c r="B132">
-        <v>327</v>
+        <v>58</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -20179,14 +20479,17 @@
         <v>11</v>
       </c>
       <c r="B133">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -20194,17 +20497,14 @@
         <v>11</v>
       </c>
       <c r="B134">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C134">
-        <v>3</v>
-      </c>
-      <c r="D134" s="2">
-        <v>1000000</v>
+        <v>6</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -20212,14 +20512,17 @@
         <v>11</v>
       </c>
       <c r="B135">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="C135">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D135" s="2">
+        <v>26000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -20227,17 +20530,17 @@
         <v>11</v>
       </c>
       <c r="B136">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="C136">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D136" s="2">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -20245,14 +20548,17 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C137">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D137" s="2">
+        <v>7500000</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -20260,17 +20566,23 @@
         <v>11</v>
       </c>
       <c r="B138">
-        <v>6</v>
+        <v>166</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D138" s="2">
-        <v>26000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="F138" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="H138" s="2">
+        <v>30000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -20278,17 +20590,17 @@
         <v>11</v>
       </c>
       <c r="B139">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="C139">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D139" s="2">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -20296,17 +20608,14 @@
         <v>11</v>
       </c>
       <c r="B140">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="C140">
-        <v>9</v>
-      </c>
-      <c r="D140" s="2">
-        <v>7500000</v>
+        <v>12</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -20314,23 +20623,14 @@
         <v>11</v>
       </c>
       <c r="B141">
-        <v>166</v>
+        <v>266</v>
       </c>
       <c r="C141">
-        <v>10</v>
-      </c>
-      <c r="D141" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="F141" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="H141" s="2">
-        <v>30000000</v>
+        <v>13</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -20338,62 +20638,74 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="C142">
-        <v>11</v>
-      </c>
-      <c r="D142" s="2">
-        <v>1000000</v>
+        <v>14</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B143">
-        <v>109</v>
+        <v>403</v>
       </c>
       <c r="C143">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F143" s="2">
+        <v>5000000</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B144">
-        <v>266</v>
+        <v>345</v>
       </c>
       <c r="C144">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="D144" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="F144" s="2">
+        <v>3500000</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B145">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="C145">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1000000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -20401,20 +20713,14 @@
         <v>12</v>
       </c>
       <c r="B146">
-        <v>403</v>
+        <v>22</v>
       </c>
       <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>5000000</v>
-      </c>
-      <c r="F146" s="2">
-        <v>5000000</v>
+        <v>4</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -20422,20 +20728,17 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>345</v>
+        <v>54</v>
       </c>
       <c r="C147">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D147" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="F147" s="2">
-        <v>3500000</v>
+        <v>11000000</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -20443,17 +20746,20 @@
         <v>12</v>
       </c>
       <c r="B148">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="C148">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D148" s="2">
-        <v>1000000</v>
+        <v>20000000</v>
+      </c>
+      <c r="F148" s="2">
+        <v>20000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -20461,14 +20767,23 @@
         <v>12</v>
       </c>
       <c r="B149">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="C149">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D149" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="F149" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="H149" s="2">
+        <v>18000000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -20476,80 +20791,68 @@
         <v>12</v>
       </c>
       <c r="B150">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D150" s="2">
-        <v>11000000</v>
+        <v>2500000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B151">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="C151">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D151" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F151" s="2">
-        <v>20000000</v>
+        <v>1000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B152">
-        <v>226</v>
+        <v>363</v>
       </c>
       <c r="C152">
-        <v>7</v>
-      </c>
-      <c r="D152" s="2">
-        <v>18000000</v>
-      </c>
-      <c r="F152" s="2">
-        <v>18000000</v>
-      </c>
-      <c r="H152" s="2">
-        <v>18000000</v>
+        <v>2</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B153">
-        <v>115</v>
+        <v>296</v>
       </c>
       <c r="C153">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D153" s="2">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -20557,17 +20860,17 @@
         <v>13</v>
       </c>
       <c r="B154">
-        <v>307</v>
+        <v>171</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D154" s="2">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -20575,14 +20878,14 @@
         <v>13</v>
       </c>
       <c r="B155">
-        <v>363</v>
+        <v>10</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -20590,17 +20893,14 @@
         <v>13</v>
       </c>
       <c r="B156">
-        <v>296</v>
+        <v>46</v>
       </c>
       <c r="C156">
-        <v>3</v>
-      </c>
-      <c r="D156" s="2">
-        <v>3000000</v>
+        <v>6</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -20608,17 +20908,17 @@
         <v>13</v>
       </c>
       <c r="B157">
-        <v>171</v>
+        <v>4</v>
       </c>
       <c r="C157">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D157" s="2">
-        <v>2000000</v>
+        <v>11500000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -20626,14 +20926,23 @@
         <v>13</v>
       </c>
       <c r="B158">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D158" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="F158" s="2">
+        <v>16000000</v>
+      </c>
+      <c r="H158" s="2">
+        <v>16000000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -20641,14 +20950,23 @@
         <v>13</v>
       </c>
       <c r="B159">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C159">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D159" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="F159" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H159" s="2">
+        <v>12000000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -20656,17 +20974,17 @@
         <v>13</v>
       </c>
       <c r="B160">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C160">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D160" s="2">
-        <v>11500000</v>
+        <v>19000000</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -20674,107 +20992,83 @@
         <v>13</v>
       </c>
       <c r="B161">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="C161">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D161" s="2">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="F161" s="2">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="H161" s="2">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B162">
-        <v>55</v>
+        <v>317</v>
       </c>
       <c r="C162">
-        <v>9</v>
-      </c>
-      <c r="D162" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="F162" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="H162" s="2">
-        <v>12000000</v>
+        <v>1</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B163">
-        <v>66</v>
+        <v>299</v>
       </c>
       <c r="C163">
-        <v>10</v>
-      </c>
-      <c r="D163" s="2">
-        <v>19000000</v>
+        <v>2</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B164">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C164">
-        <v>11</v>
-      </c>
-      <c r="D164" s="2">
-        <v>1000000</v>
+        <v>3</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Zach Collins</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B165">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="C165">
-        <v>12</v>
-      </c>
-      <c r="D165" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="F165" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="H165" s="2">
-        <v>6000000</v>
+        <v>4</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -20782,14 +21076,17 @@
         <v>14</v>
       </c>
       <c r="B166">
-        <v>317</v>
+        <v>24</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D166" s="2">
+        <v>1000000</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -20797,14 +21094,17 @@
         <v>14</v>
       </c>
       <c r="B167">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D167" s="2">
+        <v>3000000</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -20812,14 +21112,23 @@
         <v>14</v>
       </c>
       <c r="B168">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="C168">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="D168" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="F168" s="2">
+        <v>20500000</v>
+      </c>
+      <c r="H168" s="2">
+        <v>20500000</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -20827,14 +21136,17 @@
         <v>14</v>
       </c>
       <c r="B169">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C169">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="D169" s="2">
+        <v>19500000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -20842,17 +21154,29 @@
         <v>14</v>
       </c>
       <c r="B170">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C170">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D170" s="2">
-        <v>1000000</v>
+        <v>9500000</v>
+      </c>
+      <c r="F170" s="2">
+        <v>10500000</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H170" s="2">
+        <v>11500000</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -20860,17 +21184,14 @@
         <v>14</v>
       </c>
       <c r="B171">
-        <v>238</v>
+        <v>2</v>
       </c>
       <c r="C171">
-        <v>6</v>
-      </c>
-      <c r="D171" s="2">
-        <v>3000000</v>
+        <v>10</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -20878,23 +21199,14 @@
         <v>14</v>
       </c>
       <c r="B172">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="C172">
-        <v>7</v>
-      </c>
-      <c r="D172" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="F172" s="2">
-        <v>20500000</v>
-      </c>
-      <c r="H172" s="2">
-        <v>20500000</v>
+        <v>11</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -20902,17 +21214,23 @@
         <v>14</v>
       </c>
       <c r="B173">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="C173">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D173" s="2">
-        <v>19500000</v>
+        <v>20000000</v>
+      </c>
+      <c r="F173" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H173" s="2">
+        <v>20000000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>LaMelo Ball</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -20920,83 +21238,20 @@
         <v>14</v>
       </c>
       <c r="B174">
-        <v>61</v>
+        <v>273</v>
       </c>
       <c r="C174">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D174" s="2">
-        <v>9500000</v>
+        <v>3200000</v>
       </c>
       <c r="F174" s="2">
-        <v>10500000</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H174" s="2">
-        <v>11500000</v>
-      </c>
-      <c r="I174" s="2" t="s">
-        <v>472</v>
+        <v>3500000</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175">
-        <v>14</v>
-      </c>
-      <c r="B175">
-        <v>2</v>
-      </c>
-      <c r="C175">
-        <v>10</v>
-      </c>
-      <c r="L175" t="str">
-        <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176">
-        <v>14</v>
-      </c>
-      <c r="B176">
-        <v>220</v>
-      </c>
-      <c r="C176">
-        <v>11</v>
-      </c>
-      <c r="L176" t="str">
-        <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>14</v>
-      </c>
-      <c r="B177">
-        <v>145</v>
-      </c>
-      <c r="C177">
-        <v>12</v>
-      </c>
-      <c r="D177" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F177" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="H177" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="L177" t="str">
-        <f>VLOOKUP(B177,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Cason Wallace</v>
       </c>
     </row>
   </sheetData>
@@ -21007,7 +21262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B357A823-6505-4984-ACC9-40636E218B6C}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
@@ -21273,88 +21528,86 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>377</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2">
-        <v>1000000</v>
+        <v>6500000</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H9" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" t="str">
         <f>VLOOKUP(B9,players!A:B,2)</f>
-        <v>Nikola Topić</v>
+        <v>Zach Edey</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>408</v>
+        <v>290</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2">
-        <v>3400000</v>
+        <v>1000000</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
-        <v>3700000</v>
+        <v>1000000</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2">
+        <v>1000000</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" t="str">
         <f>VLOOKUP(B10,players!A:B,2)</f>
-        <v>Jase Richardson</v>
+        <v>Will Riley</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2">
-        <v>6500000</v>
+        <v>3200000</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2">
-        <v>7000000</v>
+        <v>3400000</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H11" s="2">
-        <v>7500000</v>
+        <v>3700000</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>472</v>
@@ -21363,18 +21616,18 @@
       <c r="K11" s="2"/>
       <c r="L11" t="str">
         <f>VLOOKUP(B11,players!A:B,2)</f>
-        <v>VJ Edgecombe</v>
+        <v>Derik Queen</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12">
-        <v>139</v>
+        <v>377</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
         <v>1000000</v>
@@ -21396,40 +21649,36 @@
       <c r="K12" s="2"/>
       <c r="L12" t="str">
         <f>VLOOKUP(B12,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>Nikola Topić</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13">
-        <v>209</v>
+        <v>408</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>1000000</v>
+        <v>3400000</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
-        <v>1000000</v>
+        <v>3700000</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H13" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" t="str">
         <f>VLOOKUP(B13,players!A:B,2)</f>
-        <v>Nique Clifford</v>
+        <v>Jase Richardson</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -21437,23 +21686,23 @@
         <v>5</v>
       </c>
       <c r="B14">
-        <v>409</v>
+        <v>92</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>4000000</v>
+        <v>6500000</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2">
-        <v>4200000</v>
+        <v>7000000</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H14" s="2">
-        <v>4500000</v>
+        <v>7500000</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>472</v>
@@ -21462,109 +21711,113 @@
       <c r="K14" s="2"/>
       <c r="L14" t="str">
         <f>VLOOKUP(B14,players!A:B,2)</f>
-        <v>Hansen Yang</v>
+        <v>VJ Edgecombe</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>133</v>
+      </c>
+      <c r="C15">
         <v>6</v>
       </c>
-      <c r="B15">
-        <v>192</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
       <c r="D15" s="2">
-        <v>3200000</v>
+        <v>2800000</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2">
-        <v>3500000</v>
+        <v>3000000</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="H15" s="2">
+        <v>3300000</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" t="str">
         <f>VLOOKUP(B15,players!A:B,2)</f>
-        <v>Tidjane Salaün</v>
+        <v>Collin Murray-Boyles</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B16">
-        <v>47</v>
+        <v>409</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2">
-        <v>1000000</v>
+        <v>4200000</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="H16" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" t="str">
         <f>VLOOKUP(B16,players!A:B,2)</f>
-        <v>Kyle Filipowski</v>
+        <v>Hansen Yang</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>5000000</v>
+        <v>3200000</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2">
-        <v>5500000</v>
+        <v>3500000</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H17" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" t="str">
         <f>VLOOKUP(B17,players!A:B,2)</f>
-        <v>Kon Knueppel</v>
+        <v>Tidjane Salaün</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2">
         <v>1000000</v>
@@ -21582,7 +21835,7 @@
       <c r="K18" s="2"/>
       <c r="L18" t="str">
         <f>VLOOKUP(B18,players!A:B,2)</f>
-        <v>Jaylon Tyson</v>
+        <v>Kyle Filipowski</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -21590,72 +21843,72 @@
         <v>9</v>
       </c>
       <c r="B19">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2">
-        <v>1000000</v>
+        <v>5500000</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="H19" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" t="str">
         <f>VLOOKUP(B19,players!A:B,2)</f>
-        <v>Joan Beringer</v>
+        <v>Kon Knueppel</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20">
-        <v>297</v>
+        <v>123</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>5500000</v>
+        <v>1000000</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H20" s="2">
-        <v>6500000</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" t="str">
         <f>VLOOKUP(B20,players!A:B,2)</f>
-        <v>Tre Johnson</v>
+        <v>Jaylon Tyson</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21">
-        <v>313</v>
+        <v>410</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
         <v>1000000</v>
@@ -21664,14 +21917,16 @@
       <c r="F21" s="2">
         <v>1000000</v>
       </c>
-      <c r="G21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" t="str">
         <f>VLOOKUP(B21,players!A:B,2)</f>
-        <v>Ja'Kobe Walter</v>
+        <v>Joan Beringer</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -21679,24 +21934,32 @@
         <v>10</v>
       </c>
       <c r="B22">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2">
         <v>6000000</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H22" s="2">
+        <v>6500000</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" t="str">
         <f>VLOOKUP(B22,players!A:B,2)</f>
-        <v>Cam Whitmore</v>
+        <v>Tre Johnson</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -21704,10 +21967,10 @@
         <v>10</v>
       </c>
       <c r="B23">
-        <v>411</v>
+        <v>313</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
         <v>1000000</v>
@@ -21716,74 +21979,72 @@
       <c r="F23" s="2">
         <v>1000000</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H23" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" t="str">
         <f>VLOOKUP(B23,players!A:B,2)</f>
-        <v>Thomas Sorber</v>
+        <v>Ja'Kobe Walter</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24">
-        <v>412</v>
+        <v>300</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>3200000</v>
+        <v>6000000</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" t="str">
         <f>VLOOKUP(B24,players!A:B,2)</f>
-        <v>Carter Bryant</v>
+        <v>Cam Whitmore</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>3300000</v>
+        <v>1000000</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="F25" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" t="str">
         <f>VLOOKUP(B25,players!A:B,2)</f>
-        <v>Dalton Knecht</v>
+        <v>Thomas Sorber</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -21791,86 +22052,78 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>189</v>
+        <v>412</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>6000000</v>
+        <v>3200000</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="F26" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" t="str">
         <f>VLOOKUP(B26,players!A:B,2)</f>
-        <v>Ron Holland</v>
+        <v>Carter Bryant</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B27">
-        <v>252</v>
+        <v>413</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2">
-        <v>1000000</v>
+        <v>3300000</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" t="str">
         <f>VLOOKUP(B27,players!A:B,2)</f>
-        <v>Devin Carter</v>
+        <v>Dalton Knecht</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28">
-        <v>414</v>
+        <v>189</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2">
-        <v>3600000</v>
+        <v>6000000</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2">
-        <v>3800000</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H28" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" t="str">
         <f>VLOOKUP(B28,players!A:B,2)</f>
-        <v>Kaman Maluach</v>
+        <v>Ron Holland</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -21878,84 +22131,94 @@
         <v>13</v>
       </c>
       <c r="B29">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>8500000</v>
+        <v>1000000</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2">
-        <v>9250000</v>
+        <v>1000000</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H29" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" t="str">
         <f>VLOOKUP(B29,players!A:B,2)</f>
-        <v>Dylan Harper</v>
+        <v>Devin Carter</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30">
-        <v>273</v>
+        <v>414</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2">
-        <v>3200000</v>
+        <v>3600000</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2">
-        <v>3500000</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+        <v>3800000</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H30" s="2">
+        <v>4100000</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>Kaman Maluach</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
-        <v>1000000</v>
+        <v>8500000</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="F31" s="2">
+        <v>9250000</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H31" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>472</v>
+      </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Jaylen Wells</v>
+        <v>Dylan Harper</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -21963,31 +22226,56 @@
         <v>14</v>
       </c>
       <c r="B32">
-        <v>415</v>
+        <v>259</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2">
-        <v>3800000</v>
+        <v>1000000</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="2">
-        <v>4000000</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H32" s="2">
-        <v>4200000</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
+        <v>Jaylen Wells</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>14</v>
+      </c>
+      <c r="B33">
+        <v>415</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4200000</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" t="str">
+        <f>VLOOKUP(B33,players!A:B,2)</f>
         <v>Noah Essengue</v>
       </c>
     </row>
@@ -21998,10 +22286,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD8F2BA-1077-4C4D-A103-CA2B53B5C282}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -22036,6 +22328,1893 @@
       </c>
       <c r="E2">
         <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2026</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>526</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2028</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2028</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>528</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2029</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>2029</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2026</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>531</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2026</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>532</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2026</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>533</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>2026</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>534</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>2026</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>535</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>2027</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>536</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>2027</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>537</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>2027</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>538</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>2027</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>539</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>2028</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>540</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>2028</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>541</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>2029</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>542</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>2029</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>543</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>2026</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>544</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>2026</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>545</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>2027</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>546</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>2028</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>548</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>2028</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>547</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>2029</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>549</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>2029</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>550</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>2026</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>551</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>2027</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>552</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>2027</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>553</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>2028</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>554</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>2028</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>555</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>2029</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>556</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>2029</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>557</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>2026</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>559</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>2027</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>558</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>2027</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>560</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>2028</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>561</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>2028</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>562</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>2029</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>563</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>2029</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>564</v>
+      </c>
+      <c r="B43">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>2026</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>565</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>2026</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>566</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>2026</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>567</v>
+      </c>
+      <c r="B46">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>2026</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>569</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>2027</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>570</v>
+      </c>
+      <c r="B48">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>2027</v>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>571</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>2028</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>572</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>2029</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>573</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>2029</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>574</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>2026</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>568</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>2026</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>575</v>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>2026</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>576</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>2027</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>577</v>
+      </c>
+      <c r="B56">
+        <v>6</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>2028</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>579</v>
+      </c>
+      <c r="B57">
+        <v>5</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>2028</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>578</v>
+      </c>
+      <c r="B58">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>2029</v>
+      </c>
+      <c r="E58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>580</v>
+      </c>
+      <c r="B59">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>2029</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>581</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>2026</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>582</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>2026</v>
+      </c>
+      <c r="E61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>583</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>2026</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>584</v>
+      </c>
+      <c r="B63">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>2027</v>
+      </c>
+      <c r="E63">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>585</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>2027</v>
+      </c>
+      <c r="E64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>586</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>2028</v>
+      </c>
+      <c r="E65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>587</v>
+      </c>
+      <c r="B66">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>2028</v>
+      </c>
+      <c r="E66">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>588</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>2028</v>
+      </c>
+      <c r="E67">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>589</v>
+      </c>
+      <c r="B68">
+        <v>8</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>2029</v>
+      </c>
+      <c r="E68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>590</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69">
+        <v>2029</v>
+      </c>
+      <c r="E69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>591</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>2026</v>
+      </c>
+      <c r="E70">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>592</v>
+      </c>
+      <c r="B71">
+        <v>9</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>2027</v>
+      </c>
+      <c r="E71">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>593</v>
+      </c>
+      <c r="B72">
+        <v>9</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>2027</v>
+      </c>
+      <c r="E72">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>594</v>
+      </c>
+      <c r="B73">
+        <v>9</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>2028</v>
+      </c>
+      <c r="E73">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>595</v>
+      </c>
+      <c r="B74">
+        <v>9</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>2028</v>
+      </c>
+      <c r="E74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>596</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>2029</v>
+      </c>
+      <c r="E75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>597</v>
+      </c>
+      <c r="B76">
+        <v>9</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>2029</v>
+      </c>
+      <c r="E76">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>598</v>
+      </c>
+      <c r="B77">
+        <v>13</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>2026</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>604</v>
+      </c>
+      <c r="B78">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>2027</v>
+      </c>
+      <c r="E78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>599</v>
+      </c>
+      <c r="B79">
+        <v>10</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>2027</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>605</v>
+      </c>
+      <c r="B80">
+        <v>10</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>2027</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>600</v>
+      </c>
+      <c r="B81">
+        <v>10</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>2028</v>
+      </c>
+      <c r="E81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>603</v>
+      </c>
+      <c r="B82">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <v>2028</v>
+      </c>
+      <c r="E82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>601</v>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>2029</v>
+      </c>
+      <c r="E83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>602</v>
+      </c>
+      <c r="B84">
+        <v>10</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84">
+        <v>2029</v>
+      </c>
+      <c r="E84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>606</v>
+      </c>
+      <c r="B85">
+        <v>11</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85">
+        <v>2026</v>
+      </c>
+      <c r="E85">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>610</v>
+      </c>
+      <c r="B86">
+        <v>11</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>2027</v>
+      </c>
+      <c r="E86">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>609</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>2027</v>
+      </c>
+      <c r="E87">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>611</v>
+      </c>
+      <c r="B88">
+        <v>11</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>2028</v>
+      </c>
+      <c r="E88">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>608</v>
+      </c>
+      <c r="B89">
+        <v>11</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89">
+        <v>2028</v>
+      </c>
+      <c r="E89">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>612</v>
+      </c>
+      <c r="B90">
+        <v>11</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>2029</v>
+      </c>
+      <c r="E90">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>607</v>
+      </c>
+      <c r="B91">
+        <v>11</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>2029</v>
+      </c>
+      <c r="E91">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>613</v>
+      </c>
+      <c r="B92">
+        <v>12</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>2026</v>
+      </c>
+      <c r="E92">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>614</v>
+      </c>
+      <c r="B93">
+        <v>12</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>2026</v>
+      </c>
+      <c r="E93">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>615</v>
+      </c>
+      <c r="B94">
+        <v>12</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>2027</v>
+      </c>
+      <c r="E94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>616</v>
+      </c>
+      <c r="B95">
+        <v>12</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95">
+        <v>2027</v>
+      </c>
+      <c r="E95">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>617</v>
+      </c>
+      <c r="B96">
+        <v>12</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>2028</v>
+      </c>
+      <c r="E96">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>618</v>
+      </c>
+      <c r="B97">
+        <v>12</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97">
+        <v>2028</v>
+      </c>
+      <c r="E97">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>619</v>
+      </c>
+      <c r="B98">
+        <v>12</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>2029</v>
+      </c>
+      <c r="E98">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>620</v>
+      </c>
+      <c r="B99">
+        <v>12</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>2029</v>
+      </c>
+      <c r="E99">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>621</v>
+      </c>
+      <c r="B100">
+        <v>4</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>2026</v>
+      </c>
+      <c r="E100">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>622</v>
+      </c>
+      <c r="B101">
+        <v>13</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>2027</v>
+      </c>
+      <c r="E101">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>623</v>
+      </c>
+      <c r="B102">
+        <v>13</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>2027</v>
+      </c>
+      <c r="E102">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>624</v>
+      </c>
+      <c r="B103">
+        <v>13</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>2028</v>
+      </c>
+      <c r="E103">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>625</v>
+      </c>
+      <c r="B104">
+        <v>13</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104">
+        <v>2028</v>
+      </c>
+      <c r="E104">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>626</v>
+      </c>
+      <c r="B105">
+        <v>13</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>2029</v>
+      </c>
+      <c r="E105">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>627</v>
+      </c>
+      <c r="B106">
+        <v>13</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="D106">
+        <v>2029</v>
+      </c>
+      <c r="E106">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>628</v>
+      </c>
+      <c r="B107">
+        <v>14</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>2027</v>
+      </c>
+      <c r="E107">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>629</v>
+      </c>
+      <c r="B108">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108">
+        <v>2027</v>
+      </c>
+      <c r="E108">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>630</v>
+      </c>
+      <c r="B109">
+        <v>2</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+      <c r="D109">
+        <v>2027</v>
+      </c>
+      <c r="E109">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>631</v>
+      </c>
+      <c r="B110">
+        <v>14</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>2028</v>
+      </c>
+      <c r="E110">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>632</v>
+      </c>
+      <c r="B111">
+        <v>14</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <v>2028</v>
+      </c>
+      <c r="E111">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>633</v>
+      </c>
+      <c r="B112">
+        <v>14</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>2029</v>
+      </c>
+      <c r="E112">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>634</v>
+      </c>
+      <c r="B113">
+        <v>14</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113">
+        <v>2029</v>
+      </c>
+      <c r="E113">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -22045,8 +24224,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D71993F-8E81-4064-B756-2C14E71F7CC9}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -22067,6 +24252,161 @@
       <c r="F1" s="2" t="s">
         <v>478</v>
       </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1638000</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <f>1050000+150000</f>
+        <v>1200000</v>
+      </c>
+      <c r="C6" s="2">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>750000</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>150000</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>600000</v>
+      </c>
+      <c r="C15" s="2">
+        <v>600000</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Fantasy unificado/roster.xlsx
+++ b/Fantasy unificado/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{860EFEF1-6104-4D29-9D31-1B3D52A618E7}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43C45123-7EB4-477F-8C0F-7C1A0BE0E23E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="729">
   <si>
     <t>team_id</t>
   </si>
@@ -2200,6 +2200,39 @@
   </si>
   <si>
     <t>P2029_R2_T14</t>
+  </si>
+  <si>
+    <t>Brayden Burries</t>
+  </si>
+  <si>
+    <t>Aday Mara</t>
+  </si>
+  <si>
+    <t>Yaxel Lendeborg</t>
+  </si>
+  <si>
+    <t>Cameron Carr</t>
+  </si>
+  <si>
+    <t>Nate Ament</t>
+  </si>
+  <si>
+    <t>Dailyn Swain</t>
+  </si>
+  <si>
+    <t>Ebuka Okorie</t>
+  </si>
+  <si>
+    <t>Allen Graves</t>
+  </si>
+  <si>
+    <t>Meleek Thomas</t>
+  </si>
+  <si>
+    <t>Bruce Thornton</t>
+  </si>
+  <si>
+    <t>Labaron Philon Jr.</t>
   </si>
 </sst>
 </file>
@@ -2280,6 +2313,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2599,7 +2636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M427"/>
+  <dimension ref="A1:M438"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -16325,6 +16362,358 @@
         <v>0</v>
       </c>
       <c r="K427" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E428" s="1">
+        <v>0</v>
+      </c>
+      <c r="F428" s="1">
+        <v>0</v>
+      </c>
+      <c r="G428" s="1">
+        <v>0</v>
+      </c>
+      <c r="H428" s="1">
+        <v>0</v>
+      </c>
+      <c r="I428" s="1">
+        <v>0</v>
+      </c>
+      <c r="J428" s="1">
+        <v>0</v>
+      </c>
+      <c r="K428" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E429" s="1">
+        <v>0</v>
+      </c>
+      <c r="F429" s="1">
+        <v>0</v>
+      </c>
+      <c r="G429" s="1">
+        <v>0</v>
+      </c>
+      <c r="H429" s="1">
+        <v>0</v>
+      </c>
+      <c r="I429" s="1">
+        <v>0</v>
+      </c>
+      <c r="J429" s="1">
+        <v>0</v>
+      </c>
+      <c r="K429" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E430" s="1">
+        <v>0</v>
+      </c>
+      <c r="F430" s="1">
+        <v>0</v>
+      </c>
+      <c r="G430" s="1">
+        <v>0</v>
+      </c>
+      <c r="H430" s="1">
+        <v>0</v>
+      </c>
+      <c r="I430" s="1">
+        <v>0</v>
+      </c>
+      <c r="J430" s="1">
+        <v>0</v>
+      </c>
+      <c r="K430" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E431" s="1">
+        <v>0</v>
+      </c>
+      <c r="F431" s="1">
+        <v>0</v>
+      </c>
+      <c r="G431" s="1">
+        <v>0</v>
+      </c>
+      <c r="H431" s="1">
+        <v>0</v>
+      </c>
+      <c r="I431" s="1">
+        <v>0</v>
+      </c>
+      <c r="J431" s="1">
+        <v>0</v>
+      </c>
+      <c r="K431" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E432" s="1">
+        <v>0</v>
+      </c>
+      <c r="F432" s="1">
+        <v>0</v>
+      </c>
+      <c r="G432" s="1">
+        <v>0</v>
+      </c>
+      <c r="H432" s="1">
+        <v>0</v>
+      </c>
+      <c r="I432" s="1">
+        <v>0</v>
+      </c>
+      <c r="J432" s="1">
+        <v>0</v>
+      </c>
+      <c r="K432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E433" s="1">
+        <v>0</v>
+      </c>
+      <c r="F433" s="1">
+        <v>0</v>
+      </c>
+      <c r="G433" s="1">
+        <v>0</v>
+      </c>
+      <c r="H433" s="1">
+        <v>0</v>
+      </c>
+      <c r="I433" s="1">
+        <v>0</v>
+      </c>
+      <c r="J433" s="1">
+        <v>0</v>
+      </c>
+      <c r="K433" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E434" s="1">
+        <v>0</v>
+      </c>
+      <c r="F434" s="1">
+        <v>0</v>
+      </c>
+      <c r="G434" s="1">
+        <v>0</v>
+      </c>
+      <c r="H434" s="1">
+        <v>0</v>
+      </c>
+      <c r="I434" s="1">
+        <v>0</v>
+      </c>
+      <c r="J434" s="1">
+        <v>0</v>
+      </c>
+      <c r="K434" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E435" s="1">
+        <v>0</v>
+      </c>
+      <c r="F435" s="1">
+        <v>0</v>
+      </c>
+      <c r="G435" s="1">
+        <v>0</v>
+      </c>
+      <c r="H435" s="1">
+        <v>0</v>
+      </c>
+      <c r="I435" s="1">
+        <v>0</v>
+      </c>
+      <c r="J435" s="1">
+        <v>0</v>
+      </c>
+      <c r="K435" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E436" s="1">
+        <v>0</v>
+      </c>
+      <c r="F436" s="1">
+        <v>0</v>
+      </c>
+      <c r="G436" s="1">
+        <v>0</v>
+      </c>
+      <c r="H436" s="1">
+        <v>0</v>
+      </c>
+      <c r="I436" s="1">
+        <v>0</v>
+      </c>
+      <c r="J436" s="1">
+        <v>0</v>
+      </c>
+      <c r="K436" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>436</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E437" s="1">
+        <v>0</v>
+      </c>
+      <c r="F437" s="1">
+        <v>0</v>
+      </c>
+      <c r="G437" s="1">
+        <v>0</v>
+      </c>
+      <c r="H437" s="1">
+        <v>0</v>
+      </c>
+      <c r="I437" s="1">
+        <v>0</v>
+      </c>
+      <c r="J437" s="1">
+        <v>0</v>
+      </c>
+      <c r="K437" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>437</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E438" s="1">
+        <v>0</v>
+      </c>
+      <c r="F438" s="1">
+        <v>0</v>
+      </c>
+      <c r="G438" s="1">
+        <v>0</v>
+      </c>
+      <c r="H438" s="1">
+        <v>0</v>
+      </c>
+      <c r="I438" s="1">
+        <v>0</v>
+      </c>
+      <c r="J438" s="1">
+        <v>0</v>
+      </c>
+      <c r="K438" s="1">
         <v>0</v>
       </c>
     </row>
@@ -16340,7 +16729,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -16623,29 +17012,32 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>49</v>
+        <v>423</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
       <c r="D11">
-        <v>3200000</v>
+        <v>4000000</v>
       </c>
       <c r="F11">
-        <v>3400000</v>
-      </c>
-      <c r="G11" t="s">
-        <v>12</v>
+        <v>4500000</v>
       </c>
       <c r="H11">
-        <v>3700000</v>
+        <v>5000000</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
       </c>
+      <c r="J11">
+        <v>5500000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
       <c r="L11" t="str">
         <f>VLOOKUP(B11,players!A:B,2)</f>
-        <v>Derik Queen</v>
+        <v>Mikel Brown Jr.</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -17217,7 +17609,7 @@
         <v>421</v>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>5000000</v>
@@ -17240,6 +17632,72 @@
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
         <v>Darius Acuff</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>435</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35">
+        <v>1000000</v>
+      </c>
+      <c r="F35">
+        <v>1000000</v>
+      </c>
+      <c r="H35">
+        <v>1000000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35">
+        <v>1000000</v>
+      </c>
+      <c r="K35" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" t="str">
+        <f>VLOOKUP(B35,players!A:B,2)</f>
+        <v>Labaron Philon Jr.</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>437</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>1000000</v>
+      </c>
+      <c r="F36">
+        <v>1000000</v>
+      </c>
+      <c r="H36">
+        <v>1000000</v>
+      </c>
+      <c r="I36" t="s">
+        <v>12</v>
+      </c>
+      <c r="J36">
+        <v>1000000</v>
+      </c>
+      <c r="K36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L36" t="str">
+        <f>VLOOKUP(B36,players!A:B,2)</f>
+        <v>Bruce Thornton</v>
       </c>
     </row>
   </sheetData>
@@ -24215,7 +24673,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L184"/>
+  <dimension ref="A1:L192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24517,6 +24975,39 @@
         <v>Kyle Kuzma</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>434</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>1000000</v>
+      </c>
+      <c r="F16">
+        <v>1000000</v>
+      </c>
+      <c r="H16">
+        <v>1000000</v>
+      </c>
+      <c r="I16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16">
+        <v>1000000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" t="str">
+        <f>VLOOKUP(B16,players!A:B,2)</f>
+        <v>Allen Graves</v>
+      </c>
+    </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
@@ -24786,68 +25277,68 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B30">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="C30">
         <v>14</v>
       </c>
       <c r="D30">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="F30">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="H30">
-        <v>8250000</v>
+        <v>1000000</v>
       </c>
       <c r="I30" t="s">
         <v>12</v>
       </c>
       <c r="J30">
-        <v>9000000</v>
+        <v>1000000</v>
       </c>
       <c r="K30" t="s">
         <v>12</v>
       </c>
       <c r="L30" t="str">
         <f>VLOOKUP(B30,players!A:B,2)</f>
-        <v>Cameron Boozer</v>
+        <v>Dailyn Swain</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B31">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D31">
-        <v>3800000</v>
+        <v>7000000</v>
       </c>
       <c r="F31">
-        <v>4000000</v>
+        <v>7500000</v>
       </c>
       <c r="H31">
-        <v>4200000</v>
+        <v>8250000</v>
       </c>
       <c r="I31" t="s">
         <v>12</v>
       </c>
       <c r="J31">
-        <v>4500000</v>
+        <v>9000000</v>
       </c>
       <c r="K31" t="s">
         <v>12</v>
       </c>
       <c r="L31" t="str">
         <f>VLOOKUP(B31,players!A:B,2)</f>
-        <v>Hannes Steinbach</v>
+        <v>Cameron Boozer</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -24855,56 +25346,65 @@
         <v>1</v>
       </c>
       <c r="B32">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C32">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="F32">
-        <v>3800000</v>
+        <v>4000000</v>
       </c>
       <c r="H32">
-        <v>4000000</v>
+        <v>4200000</v>
       </c>
       <c r="I32" t="s">
         <v>12</v>
       </c>
       <c r="J32">
-        <v>4300000</v>
+        <v>4500000</v>
       </c>
       <c r="K32" t="s">
         <v>12</v>
       </c>
       <c r="L32" t="str">
         <f>VLOOKUP(B32,players!A:B,2)</f>
-        <v>Keaton Wagler</v>
+        <v>Hannes Steinbach</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33">
-        <v>320</v>
+        <v>425</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D33">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="F33">
-        <v>1000000</v>
-      </c>
-      <c r="G33" t="s">
+        <v>3800000</v>
+      </c>
+      <c r="H33">
+        <v>4000000</v>
+      </c>
+      <c r="I33" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33">
+        <v>4300000</v>
+      </c>
+      <c r="K33" t="s">
         <v>12</v>
       </c>
       <c r="L33" t="str">
         <f>VLOOKUP(B33,players!A:B,2)</f>
-        <v>Cam Spencer</v>
+        <v>Keaton Wagler</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -24912,23 +25412,23 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>23500000</v>
+        <v>1000000</v>
       </c>
       <c r="F34">
-        <v>23500000</v>
-      </c>
-      <c r="H34">
-        <v>23500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G34" t="s">
+        <v>12</v>
       </c>
       <c r="L34" t="str">
         <f>VLOOKUP(B34,players!A:B,2)</f>
-        <v>Alperen Şengün</v>
+        <v>Cam Spencer</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -24936,17 +25436,23 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>15000000</v>
+        <v>23500000</v>
+      </c>
+      <c r="F35">
+        <v>23500000</v>
+      </c>
+      <c r="H35">
+        <v>23500000</v>
       </c>
       <c r="L35" t="str">
         <f>VLOOKUP(B35,players!A:B,2)</f>
-        <v>Kevin Durant</v>
+        <v>Alperen Şengün</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -24954,17 +25460,17 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>9000000</v>
+        <v>15000000</v>
       </c>
       <c r="L36" t="str">
         <f>VLOOKUP(B36,players!A:B,2)</f>
-        <v>Brandon Miller</v>
+        <v>Kevin Durant</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -24972,23 +25478,17 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>7000000</v>
-      </c>
-      <c r="F37">
-        <v>7000000</v>
-      </c>
-      <c r="H37">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
       <c r="L37" t="str">
         <f>VLOOKUP(B37,players!A:B,2)</f>
-        <v>Jalen Green</v>
+        <v>Brandon Miller</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -24996,20 +25496,23 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
       <c r="F38">
-        <v>6000000</v>
+        <v>7000000</v>
+      </c>
+      <c r="H38">
+        <v>7000000</v>
       </c>
       <c r="L38" t="str">
         <f>VLOOKUP(B38,players!A:B,2)</f>
-        <v>Tyler Herro</v>
+        <v>Jalen Green</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -25017,23 +25520,20 @@
         <v>2</v>
       </c>
       <c r="B39">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="F39">
-        <v>21500000</v>
-      </c>
-      <c r="H39">
-        <v>21500000</v>
+        <v>6000000</v>
       </c>
       <c r="L39" t="str">
         <f>VLOOKUP(B39,players!A:B,2)</f>
-        <v>Trae Young</v>
+        <v>Tyler Herro</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -25041,14 +25541,23 @@
         <v>2</v>
       </c>
       <c r="B40">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D40">
+        <v>21500000</v>
+      </c>
+      <c r="F40">
+        <v>21500000</v>
+      </c>
+      <c r="H40">
+        <v>21500000</v>
       </c>
       <c r="L40" t="str">
         <f>VLOOKUP(B40,players!A:B,2)</f>
-        <v>Russell Westbrook</v>
+        <v>Trae Young</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -25056,23 +25565,14 @@
         <v>2</v>
       </c>
       <c r="B41">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C41">
-        <v>10</v>
-      </c>
-      <c r="D41">
-        <v>3100000</v>
-      </c>
-      <c r="F41">
-        <v>3100000</v>
-      </c>
-      <c r="H41">
-        <v>3100000</v>
+        <v>8</v>
       </c>
       <c r="L41" t="str">
         <f>VLOOKUP(B41,players!A:B,2)</f>
-        <v>Bobby Portis</v>
+        <v>Russell Westbrook</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -25080,53 +25580,53 @@
         <v>2</v>
       </c>
       <c r="B42">
-        <v>423</v>
+        <v>69</v>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>4000000</v>
+        <v>3100000</v>
       </c>
       <c r="F42">
-        <v>4500000</v>
+        <v>3100000</v>
       </c>
       <c r="H42">
-        <v>5000000</v>
-      </c>
-      <c r="I42" t="s">
-        <v>12</v>
-      </c>
-      <c r="J42">
-        <v>5500000</v>
-      </c>
-      <c r="K42" t="s">
-        <v>12</v>
+        <v>3100000</v>
       </c>
       <c r="L42" t="str">
         <f>VLOOKUP(B42,players!A:B,2)</f>
-        <v>Mikel Brown Jr.</v>
+        <v>Bobby Portis</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D43">
-        <v>8000000</v>
+        <v>3200000</v>
       </c>
       <c r="F43">
-        <v>8000000</v>
+        <v>3400000</v>
+      </c>
+      <c r="G43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43">
+        <v>3700000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>12</v>
       </c>
       <c r="L43" t="str">
         <f>VLOOKUP(B43,players!A:B,2)</f>
-        <v>Immanuel Quickley</v>
+        <v>Derik Queen</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -25134,14 +25634,20 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>8000000</v>
+      </c>
+      <c r="F44">
+        <v>8000000</v>
       </c>
       <c r="L44" t="str">
         <f>VLOOKUP(B44,players!A:B,2)</f>
-        <v>Nickeil Alexander-Walker</v>
+        <v>Immanuel Quickley</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -25149,14 +25655,14 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" t="str">
         <f>VLOOKUP(B45,players!A:B,2)</f>
-        <v>Kyshawn George</v>
+        <v>Nickeil Alexander-Walker</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -25164,17 +25670,14 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C46">
-        <v>4</v>
-      </c>
-      <c r="D46">
-        <v>5000000</v>
+        <v>3</v>
       </c>
       <c r="L46" t="str">
         <f>VLOOKUP(B46,players!A:B,2)</f>
-        <v>Cameron Johnson</v>
+        <v>Kyshawn George</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -25182,14 +25685,17 @@
         <v>3</v>
       </c>
       <c r="B47">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D47">
+        <v>5000000</v>
       </c>
       <c r="L47" t="str">
         <f>VLOOKUP(B47,players!A:B,2)</f>
-        <v>Myles Turner</v>
+        <v>Cameron Johnson</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -25197,14 +25703,14 @@
         <v>3</v>
       </c>
       <c r="B48">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L48" t="str">
         <f>VLOOKUP(B48,players!A:B,2)</f>
-        <v>Mitchell Robinson</v>
+        <v>Myles Turner</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -25212,14 +25718,14 @@
         <v>3</v>
       </c>
       <c r="B49">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L49" t="str">
         <f>VLOOKUP(B49,players!A:B,2)</f>
-        <v>Jalen Duren</v>
+        <v>Mitchell Robinson</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -25227,23 +25733,14 @@
         <v>3</v>
       </c>
       <c r="B50">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C50">
-        <v>8</v>
-      </c>
-      <c r="D50">
-        <v>40000000</v>
-      </c>
-      <c r="F50">
-        <v>40000000</v>
-      </c>
-      <c r="H50">
-        <v>40000000</v>
+        <v>7</v>
       </c>
       <c r="L50" t="str">
         <f>VLOOKUP(B50,players!A:B,2)</f>
-        <v>Luka Dončić</v>
+        <v>Jalen Duren</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -25251,17 +25748,23 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51">
-        <v>6000000</v>
+        <v>40000000</v>
+      </c>
+      <c r="F51">
+        <v>40000000</v>
+      </c>
+      <c r="H51">
+        <v>40000000</v>
       </c>
       <c r="L51" t="str">
         <f>VLOOKUP(B51,players!A:B,2)</f>
-        <v>Kawhi Leonard</v>
+        <v>Luka Dončić</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -25269,20 +25772,17 @@
         <v>3</v>
       </c>
       <c r="B52">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D52">
-        <v>14000000</v>
-      </c>
-      <c r="F52">
-        <v>14000000</v>
+        <v>6000000</v>
       </c>
       <c r="L52" t="str">
         <f>VLOOKUP(B52,players!A:B,2)</f>
-        <v>Jaren Jackson Jr.</v>
+        <v>Kawhi Leonard</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -25290,23 +25790,20 @@
         <v>3</v>
       </c>
       <c r="B53">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D53">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="F53">
-        <v>6500000</v>
-      </c>
-      <c r="H53">
-        <v>6500000</v>
+        <v>14000000</v>
       </c>
       <c r="L53" t="str">
         <f>VLOOKUP(B53,players!A:B,2)</f>
-        <v>OG Anunoby</v>
+        <v>Jaren Jackson Jr.</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -25314,17 +25811,23 @@
         <v>3</v>
       </c>
       <c r="B54">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D54">
-        <v>5000000</v>
+        <v>6500000</v>
+      </c>
+      <c r="F54">
+        <v>6500000</v>
+      </c>
+      <c r="H54">
+        <v>6500000</v>
       </c>
       <c r="L54" t="str">
         <f>VLOOKUP(B54,players!A:B,2)</f>
-        <v>Kyrie Irving</v>
+        <v>OG Anunoby</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -25332,71 +25835,68 @@
         <v>3</v>
       </c>
       <c r="B55">
-        <v>295</v>
+        <v>142</v>
       </c>
       <c r="C55">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D55">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="L55" t="str">
         <f>VLOOKUP(B55,players!A:B,2)</f>
-        <v>Zach LaVine</v>
+        <v>Kyrie Irving</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D56">
-        <v>1000000</v>
-      </c>
-      <c r="F56">
-        <v>1000000</v>
-      </c>
-      <c r="G56" t="s">
-        <v>12</v>
-      </c>
-      <c r="H56">
-        <v>1000000</v>
-      </c>
-      <c r="I56" t="s">
-        <v>12</v>
+        <v>8000000</v>
       </c>
       <c r="L56" t="str">
         <f>VLOOKUP(B56,players!A:B,2)</f>
-        <v>Nolan Traoré</v>
+        <v>Zach LaVine</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57">
-        <v>364</v>
+        <v>427</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D57">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="F57">
-        <v>1000000</v>
-      </c>
-      <c r="G57" t="s">
+        <v>3400000</v>
+      </c>
+      <c r="H57">
+        <v>3600000</v>
+      </c>
+      <c r="I57" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57">
+        <v>3900000</v>
+      </c>
+      <c r="K57" t="s">
         <v>12</v>
       </c>
       <c r="L57" t="str">
         <f>VLOOKUP(B57,players!A:B,2)</f>
-        <v>Jared McCain</v>
+        <v>Brayden Burries</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -25404,14 +25904,29 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>104</v>
+        <v>379</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>1000000</v>
+      </c>
+      <c r="F58">
+        <v>1000000</v>
+      </c>
+      <c r="G58" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58">
+        <v>1000000</v>
+      </c>
+      <c r="I58" t="s">
+        <v>12</v>
       </c>
       <c r="L58" t="str">
         <f>VLOOKUP(B58,players!A:B,2)</f>
-        <v>Keldon Johnson</v>
+        <v>Nolan Traoré</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -25419,17 +25934,23 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>62</v>
+        <v>364</v>
       </c>
       <c r="C59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>2500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F59">
+        <v>1000000</v>
+      </c>
+      <c r="G59" t="s">
+        <v>12</v>
       </c>
       <c r="L59" t="str">
         <f>VLOOKUP(B59,players!A:B,2)</f>
-        <v>Santi Aldama</v>
+        <v>Jared McCain</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -25437,17 +25958,14 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="C60">
-        <v>5</v>
-      </c>
-      <c r="D60">
-        <v>11000000</v>
+        <v>3</v>
       </c>
       <c r="L60" t="str">
         <f>VLOOKUP(B60,players!A:B,2)</f>
-        <v>Deandre Ayton</v>
+        <v>Keldon Johnson</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -25455,20 +25973,17 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D61">
-        <v>5000000</v>
-      </c>
-      <c r="F61">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="L61" t="str">
         <f>VLOOKUP(B61,players!A:B,2)</f>
-        <v>Nic Claxton</v>
+        <v>Santi Aldama</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -25476,20 +25991,17 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D62">
-        <v>17000000</v>
-      </c>
-      <c r="F62">
-        <v>17000000</v>
+        <v>11000000</v>
       </c>
       <c r="L62" t="str">
         <f>VLOOKUP(B62,players!A:B,2)</f>
-        <v>Bam Adebayo</v>
+        <v>Deandre Ayton</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -25497,17 +26009,20 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D63">
-        <v>22500000</v>
+        <v>5000000</v>
+      </c>
+      <c r="F63">
+        <v>5000000</v>
       </c>
       <c r="L63" t="str">
         <f>VLOOKUP(B63,players!A:B,2)</f>
-        <v>Jaylen Brown</v>
+        <v>Nic Claxton</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -25515,23 +26030,20 @@
         <v>4</v>
       </c>
       <c r="B64">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="C64">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D64">
-        <v>5000000</v>
+        <v>17000000</v>
       </c>
       <c r="F64">
-        <v>5500000</v>
-      </c>
-      <c r="G64" t="s">
-        <v>12</v>
+        <v>17000000</v>
       </c>
       <c r="L64" t="str">
         <f>VLOOKUP(B64,players!A:B,2)</f>
-        <v>Stephon Castle</v>
+        <v>Bam Adebayo</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -25539,23 +26051,17 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D65">
-        <v>15000000</v>
-      </c>
-      <c r="F65">
-        <v>15000000</v>
-      </c>
-      <c r="H65">
-        <v>15000000</v>
+        <v>22500000</v>
       </c>
       <c r="L65" t="str">
         <f>VLOOKUP(B65,players!A:B,2)</f>
-        <v>Franz Wagner</v>
+        <v>Jaylen Brown</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -25563,23 +26069,23 @@
         <v>4</v>
       </c>
       <c r="B66">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D66">
-        <v>19000000</v>
+        <v>5000000</v>
       </c>
       <c r="F66">
-        <v>19000000</v>
-      </c>
-      <c r="H66">
-        <v>19000000</v>
+        <v>5500000</v>
+      </c>
+      <c r="G66" t="s">
+        <v>12</v>
       </c>
       <c r="L66" t="str">
         <f>VLOOKUP(B66,players!A:B,2)</f>
-        <v>Donovan Mitchell</v>
+        <v>Stephon Castle</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -25587,17 +26093,23 @@
         <v>4</v>
       </c>
       <c r="B67">
-        <v>287</v>
+        <v>114</v>
       </c>
       <c r="C67">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D67">
-        <v>10000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="F67">
+        <v>15000000</v>
+      </c>
+      <c r="H67">
+        <v>15000000</v>
       </c>
       <c r="L67" t="str">
         <f>VLOOKUP(B67,players!A:B,2)</f>
-        <v>DeMar DeRozan</v>
+        <v>Franz Wagner</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -25605,77 +26117,74 @@
         <v>4</v>
       </c>
       <c r="B68">
-        <v>422</v>
+        <v>157</v>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D68">
-        <v>4500000</v>
+        <v>19000000</v>
       </c>
       <c r="F68">
-        <v>5000000</v>
+        <v>19000000</v>
       </c>
       <c r="H68">
-        <v>5500000</v>
-      </c>
-      <c r="I68" t="s">
-        <v>12</v>
-      </c>
-      <c r="J68">
-        <v>6000000</v>
-      </c>
-      <c r="K68" t="s">
-        <v>12</v>
+        <v>19000000</v>
       </c>
       <c r="L68" t="str">
         <f>VLOOKUP(B68,players!A:B,2)</f>
-        <v>Kingston Flemings</v>
+        <v>Donovan Mitchell</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B69">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D69">
+        <v>10000000</v>
       </c>
       <c r="L69" t="str">
         <f>VLOOKUP(B69,players!A:B,2)</f>
-        <v>Dennis Schröder</v>
+        <v>DeMar DeRozan</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70">
-        <v>262</v>
+        <v>422</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D70">
-        <v>3600000</v>
+        <v>4500000</v>
       </c>
       <c r="F70">
-        <v>3800000</v>
-      </c>
-      <c r="G70" t="s">
-        <v>12</v>
+        <v>5000000</v>
       </c>
       <c r="H70">
-        <v>4100000</v>
+        <v>5500000</v>
       </c>
       <c r="I70" t="s">
         <v>12</v>
       </c>
+      <c r="J70">
+        <v>6000000</v>
+      </c>
+      <c r="K70" t="s">
+        <v>12</v>
+      </c>
       <c r="L70" t="str">
         <f>VLOOKUP(B70,players!A:B,2)</f>
-        <v>Egor Dёmin</v>
+        <v>Kingston Flemings</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -25683,14 +26192,14 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" t="str">
         <f>VLOOKUP(B71,players!A:B,2)</f>
-        <v>Grayson Allen</v>
+        <v>Dennis Schröder</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -25698,20 +26207,29 @@
         <v>5</v>
       </c>
       <c r="B72">
-        <v>143</v>
+        <v>262</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>21000000</v>
+        <v>3600000</v>
       </c>
       <c r="F72">
-        <v>21000000</v>
+        <v>3800000</v>
+      </c>
+      <c r="G72" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72">
+        <v>4100000</v>
+      </c>
+      <c r="I72" t="s">
+        <v>12</v>
       </c>
       <c r="L72" t="str">
         <f>VLOOKUP(B72,players!A:B,2)</f>
-        <v>James Harden</v>
+        <v>Egor Dёmin</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -25719,14 +26237,14 @@
         <v>5</v>
       </c>
       <c r="B73">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L73" t="str">
         <f>VLOOKUP(B73,players!A:B,2)</f>
-        <v>Isaiah Stewart</v>
+        <v>Grayson Allen</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -25734,29 +26252,20 @@
         <v>5</v>
       </c>
       <c r="B74">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D74">
-        <v>1000000</v>
+        <v>21000000</v>
       </c>
       <c r="F74">
-        <v>1000000</v>
-      </c>
-      <c r="G74" t="s">
-        <v>12</v>
-      </c>
-      <c r="H74">
-        <v>1000000</v>
-      </c>
-      <c r="I74" t="s">
-        <v>12</v>
+        <v>21000000</v>
       </c>
       <c r="L74" t="str">
         <f>VLOOKUP(B74,players!A:B,2)</f>
-        <v>Danny Wolf</v>
+        <v>James Harden</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -25764,20 +26273,14 @@
         <v>5</v>
       </c>
       <c r="B75">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="C75">
-        <v>7</v>
-      </c>
-      <c r="D75">
-        <v>17000000</v>
-      </c>
-      <c r="F75">
-        <v>17000000</v>
+        <v>5</v>
       </c>
       <c r="L75" t="str">
         <f>VLOOKUP(B75,players!A:B,2)</f>
-        <v>Joel Embiid</v>
+        <v>Isaiah Stewart</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -25785,23 +26288,29 @@
         <v>5</v>
       </c>
       <c r="B76">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D76">
-        <v>40000000</v>
+        <v>1000000</v>
       </c>
       <c r="F76">
-        <v>40000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="G76" t="s">
+        <v>12</v>
       </c>
       <c r="H76">
-        <v>40000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I76" t="s">
+        <v>12</v>
       </c>
       <c r="L76" t="str">
         <f>VLOOKUP(B76,players!A:B,2)</f>
-        <v>Giannis Antetokounmpo</v>
+        <v>Danny Wolf</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -25809,20 +26318,20 @@
         <v>5</v>
       </c>
       <c r="B77">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="C77">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D77">
-        <v>3100000</v>
+        <v>17000000</v>
       </c>
       <c r="F77">
-        <v>3100000</v>
+        <v>17000000</v>
       </c>
       <c r="L77" t="str">
         <f>VLOOKUP(B77,players!A:B,2)</f>
-        <v>Naz Reid</v>
+        <v>Joel Embiid</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -25830,14 +26339,23 @@
         <v>5</v>
       </c>
       <c r="B78">
-        <v>227</v>
+        <v>17</v>
       </c>
       <c r="C78">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D78">
+        <v>40000000</v>
+      </c>
+      <c r="F78">
+        <v>40000000</v>
+      </c>
+      <c r="H78">
+        <v>40000000</v>
       </c>
       <c r="L78" t="str">
         <f>VLOOKUP(B78,players!A:B,2)</f>
-        <v>Jerami Grant</v>
+        <v>Giannis Antetokounmpo</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -25845,14 +26363,20 @@
         <v>5</v>
       </c>
       <c r="B79">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="D79">
+        <v>3100000</v>
+      </c>
+      <c r="F79">
+        <v>3100000</v>
       </c>
       <c r="L79" t="str">
         <f>VLOOKUP(B79,players!A:B,2)</f>
-        <v>Michael Porter Jr.</v>
+        <v>Naz Reid</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -25860,14 +26384,14 @@
         <v>5</v>
       </c>
       <c r="B80">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="C80">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L80" t="str">
         <f>VLOOKUP(B80,players!A:B,2)</f>
-        <v>Royce O'Neale</v>
+        <v>Jerami Grant</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -25875,14 +26399,14 @@
         <v>5</v>
       </c>
       <c r="B81">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="C81">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L81" t="str">
         <f>VLOOKUP(B81,players!A:B,2)</f>
-        <v>Ryan Rollins</v>
+        <v>Michael Porter Jr.</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -25890,86 +26414,95 @@
         <v>5</v>
       </c>
       <c r="B82">
-        <v>418</v>
+        <v>148</v>
       </c>
       <c r="C82">
-        <v>13</v>
-      </c>
-      <c r="D82">
-        <v>8000000</v>
-      </c>
-      <c r="F82">
-        <v>8500000</v>
-      </c>
-      <c r="H82">
-        <v>9250000</v>
-      </c>
-      <c r="I82" t="s">
-        <v>12</v>
-      </c>
-      <c r="J82">
-        <v>10000000</v>
-      </c>
-      <c r="K82" t="s">
         <v>12</v>
       </c>
       <c r="L82" t="str">
         <f>VLOOKUP(B82,players!A:B,2)</f>
-        <v>Caleb Wilson</v>
+        <v>Royce O'Neale</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B83">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83">
-        <v>6000000</v>
-      </c>
-      <c r="F83">
-        <v>6000000</v>
+        <v>12</v>
       </c>
       <c r="L83" t="str">
         <f>VLOOKUP(B83,players!A:B,2)</f>
-        <v>Derrick White</v>
+        <v>Ryan Rollins</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B84">
-        <v>338</v>
+        <v>418</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D84">
-        <v>1000000</v>
+        <v>8000000</v>
+      </c>
+      <c r="F84">
+        <v>8500000</v>
+      </c>
+      <c r="H84">
+        <v>9250000</v>
+      </c>
+      <c r="I84" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84">
+        <v>10000000</v>
+      </c>
+      <c r="K84" t="s">
+        <v>12</v>
       </c>
       <c r="L84" t="str">
         <f>VLOOKUP(B84,players!A:B,2)</f>
-        <v>D'Angelo Russell</v>
+        <v>Caleb Wilson</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B85">
-        <v>45</v>
+        <v>429</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D85">
+        <v>2800000</v>
+      </c>
+      <c r="F85">
+        <v>3000000</v>
+      </c>
+      <c r="H85">
+        <v>3200000</v>
+      </c>
+      <c r="I85" t="s">
+        <v>12</v>
+      </c>
+      <c r="J85">
+        <v>3500000</v>
+      </c>
+      <c r="K85" t="s">
+        <v>12</v>
       </c>
       <c r="L85" t="str">
         <f>VLOOKUP(B85,players!A:B,2)</f>
-        <v>Josh Hart</v>
+        <v>Yaxel Lendeborg</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -25977,14 +26510,20 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>6000000</v>
+      </c>
+      <c r="F86">
+        <v>6000000</v>
       </c>
       <c r="L86" t="str">
         <f>VLOOKUP(B86,players!A:B,2)</f>
-        <v>Tobias Harris</v>
+        <v>Derrick White</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -25992,14 +26531,17 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>98</v>
+        <v>338</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>1000000</v>
       </c>
       <c r="L87" t="str">
         <f>VLOOKUP(B87,players!A:B,2)</f>
-        <v>Draymond Green</v>
+        <v>D'Angelo Russell</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -26007,14 +26549,14 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C88">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L88" t="str">
         <f>VLOOKUP(B88,players!A:B,2)</f>
-        <v>Jusuf Nurkić</v>
+        <v>Josh Hart</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -26022,17 +26564,14 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="C89">
-        <v>7</v>
-      </c>
-      <c r="D89">
-        <v>20000000</v>
+        <v>4</v>
       </c>
       <c r="L89" t="str">
         <f>VLOOKUP(B89,players!A:B,2)</f>
-        <v>Nikola Jokić</v>
+        <v>Tobias Harris</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -26040,14 +26579,14 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L90" t="str">
         <f>VLOOKUP(B90,players!A:B,2)</f>
-        <v>Paolo Banchero</v>
+        <v>Draymond Green</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -26055,17 +26594,14 @@
         <v>6</v>
       </c>
       <c r="B91">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C91">
-        <v>9</v>
-      </c>
-      <c r="D91">
-        <v>7000000</v>
+        <v>6</v>
       </c>
       <c r="L91" t="str">
         <f>VLOOKUP(B91,players!A:B,2)</f>
-        <v>Miles Bridges</v>
+        <v>Jusuf Nurkić</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -26073,20 +26609,17 @@
         <v>6</v>
       </c>
       <c r="B92">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D92">
-        <v>35000000</v>
-      </c>
-      <c r="F92">
-        <v>35000000</v>
+        <v>20000000</v>
       </c>
       <c r="L92" t="str">
         <f>VLOOKUP(B92,players!A:B,2)</f>
-        <v>Cade Cunningham</v>
+        <v>Nikola Jokić</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -26094,20 +26627,14 @@
         <v>6</v>
       </c>
       <c r="B93">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C93">
-        <v>11</v>
-      </c>
-      <c r="D93">
-        <v>3100000</v>
-      </c>
-      <c r="F93">
-        <v>3100000</v>
+        <v>8</v>
       </c>
       <c r="L93" t="str">
         <f>VLOOKUP(B93,players!A:B,2)</f>
-        <v>Jabari Smith Jr.</v>
+        <v>Paolo Banchero</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -26115,17 +26642,17 @@
         <v>6</v>
       </c>
       <c r="B94">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="C94">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D94">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="L94" t="str">
         <f>VLOOKUP(B94,players!A:B,2)</f>
-        <v>Keyonte George</v>
+        <v>Miles Bridges</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -26133,14 +26660,20 @@
         <v>6</v>
       </c>
       <c r="B95">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="C95">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D95">
+        <v>35000000</v>
+      </c>
+      <c r="F95">
+        <v>35000000</v>
       </c>
       <c r="L95" t="str">
         <f>VLOOKUP(B95,players!A:B,2)</f>
-        <v>Damian Lillard</v>
+        <v>Cade Cunningham</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -26148,20 +26681,20 @@
         <v>6</v>
       </c>
       <c r="B96">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="C96">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D96">
-        <v>6000000</v>
+        <v>3100000</v>
       </c>
       <c r="F96">
-        <v>6000000</v>
+        <v>3100000</v>
       </c>
       <c r="L96" t="str">
         <f>VLOOKUP(B96,players!A:B,2)</f>
-        <v>Jonathan Kuminga</v>
+        <v>Jabari Smith Jr.</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -26169,116 +26702,101 @@
         <v>6</v>
       </c>
       <c r="B97">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="C97">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="D97">
+        <v>1000000</v>
       </c>
       <c r="L97" t="str">
         <f>VLOOKUP(B97,players!A:B,2)</f>
-        <v>Tari Eason</v>
+        <v>Keyonte George</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B98">
-        <v>420</v>
+        <v>161</v>
       </c>
       <c r="C98">
         <v>13</v>
       </c>
-      <c r="D98">
-        <v>6000000</v>
-      </c>
-      <c r="F98">
-        <v>6500000</v>
-      </c>
-      <c r="H98">
-        <v>7000000</v>
-      </c>
-      <c r="I98" t="s">
-        <v>12</v>
-      </c>
-      <c r="J98">
-        <v>7500000</v>
-      </c>
-      <c r="K98" t="s">
-        <v>12</v>
-      </c>
       <c r="L98" t="str">
         <f>VLOOKUP(B98,players!A:B,2)</f>
-        <v>Darryn Peterson</v>
+        <v>Damian Lillard</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B99">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D99">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F99">
-        <v>4100000</v>
-      </c>
-      <c r="G99" t="s">
-        <v>12</v>
+        <v>6000000</v>
       </c>
       <c r="L99" t="str">
         <f>VLOOKUP(B99,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Jonathan Kuminga</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B100">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L100" t="str">
         <f>VLOOKUP(B100,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Tari Eason</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B101">
-        <v>76</v>
+        <v>420</v>
       </c>
       <c r="C101">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D101">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="F101">
-        <v>1000000</v>
-      </c>
-      <c r="G101" t="s">
-        <v>12</v>
+        <v>6500000</v>
       </c>
       <c r="H101">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="I101" t="s">
         <v>12</v>
       </c>
+      <c r="J101">
+        <v>7500000</v>
+      </c>
+      <c r="K101" t="s">
+        <v>12</v>
+      </c>
       <c r="L101" t="str">
         <f>VLOOKUP(B101,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Darryn Peterson</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -26286,17 +26804,23 @@
         <v>8</v>
       </c>
       <c r="B102">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D102">
-        <v>2000000</v>
+        <v>3800000</v>
+      </c>
+      <c r="F102">
+        <v>4100000</v>
+      </c>
+      <c r="G102" t="s">
+        <v>12</v>
       </c>
       <c r="L102" t="str">
         <f>VLOOKUP(B102,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -26304,23 +26828,14 @@
         <v>8</v>
       </c>
       <c r="B103">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C103">
-        <v>5</v>
-      </c>
-      <c r="D103">
-        <v>6000000</v>
-      </c>
-      <c r="F103">
-        <v>6000000</v>
-      </c>
-      <c r="H103">
-        <v>6000000</v>
+        <v>2</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -26328,23 +26843,29 @@
         <v>8</v>
       </c>
       <c r="B104">
+        <v>76</v>
+      </c>
+      <c r="C104">
         <v>3</v>
       </c>
-      <c r="C104">
-        <v>6</v>
-      </c>
       <c r="D104">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="F104">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="G104" t="s">
         <v>12</v>
       </c>
+      <c r="H104">
+        <v>1000000</v>
+      </c>
+      <c r="I104" t="s">
+        <v>12</v>
+      </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -26352,20 +26873,17 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D105">
-        <v>4000000</v>
-      </c>
-      <c r="F105">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -26373,23 +26891,23 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="C106">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D106">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="F106">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="H106">
-        <v>16000000</v>
+        <v>6000000</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -26397,20 +26915,23 @@
         <v>8</v>
       </c>
       <c r="B107">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="C107">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D107">
-        <v>9000000</v>
+        <v>7000000</v>
       </c>
       <c r="F107">
-        <v>9000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G107" t="s">
+        <v>12</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -26418,17 +26939,20 @@
         <v>8</v>
       </c>
       <c r="B108">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="C108">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D108">
-        <v>16000000</v>
+        <v>4000000</v>
+      </c>
+      <c r="F108">
+        <v>4000000</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -26436,23 +26960,23 @@
         <v>8</v>
       </c>
       <c r="B109">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="C109">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D109">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="F109">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="H109">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -26460,14 +26984,20 @@
         <v>8</v>
       </c>
       <c r="B110">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="C110">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="D110">
+        <v>9000000</v>
+      </c>
+      <c r="F110">
+        <v>9000000</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -26475,14 +27005,17 @@
         <v>8</v>
       </c>
       <c r="B111">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C111">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D111">
+        <v>16000000</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -26490,86 +27023,101 @@
         <v>8</v>
       </c>
       <c r="B112">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="C112">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="D112">
+        <v>19000000</v>
+      </c>
+      <c r="F112">
+        <v>19000000</v>
+      </c>
+      <c r="H112">
+        <v>19000000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B113">
-        <v>384</v>
+        <v>225</v>
       </c>
       <c r="C113">
-        <v>1</v>
-      </c>
-      <c r="D113">
-        <v>3100000</v>
-      </c>
-      <c r="F113">
-        <v>3100000</v>
-      </c>
-      <c r="H113">
-        <v>3100000</v>
+        <v>12</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B114">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B115">
-        <v>186</v>
+        <v>336</v>
       </c>
       <c r="C115">
-        <v>3</v>
-      </c>
-      <c r="D115">
-        <v>4500000</v>
+        <v>14</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B116">
-        <v>251</v>
+        <v>428</v>
       </c>
       <c r="C116">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="D116">
+        <v>3000000</v>
+      </c>
+      <c r="F116">
+        <v>3200000</v>
+      </c>
+      <c r="H116">
+        <v>3400000</v>
+      </c>
+      <c r="I116" t="s">
+        <v>12</v>
+      </c>
+      <c r="J116">
+        <v>3700000</v>
+      </c>
+      <c r="K116" t="s">
+        <v>12</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Aday Mara</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -26577,14 +27125,23 @@
         <v>9</v>
       </c>
       <c r="B117">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>3100000</v>
+      </c>
+      <c r="F117">
+        <v>3100000</v>
+      </c>
+      <c r="H117">
+        <v>3100000</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -26592,23 +27149,14 @@
         <v>9</v>
       </c>
       <c r="B118">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="C118">
-        <v>6</v>
-      </c>
-      <c r="D118">
-        <v>3100000</v>
-      </c>
-      <c r="F118">
-        <v>3100000</v>
-      </c>
-      <c r="H118">
-        <v>3100000</v>
+        <v>2</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -26616,23 +27164,17 @@
         <v>9</v>
       </c>
       <c r="B119">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D119">
-        <v>32000000</v>
-      </c>
-      <c r="F119">
-        <v>32000000</v>
-      </c>
-      <c r="H119">
-        <v>32000000</v>
+        <v>4500000</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -26640,23 +27182,14 @@
         <v>9</v>
       </c>
       <c r="B120">
-        <v>26</v>
+        <v>251</v>
       </c>
       <c r="C120">
-        <v>8</v>
-      </c>
-      <c r="D120">
-        <v>12500000</v>
-      </c>
-      <c r="F120">
-        <v>12500000</v>
-      </c>
-      <c r="H120">
-        <v>12500000</v>
+        <v>4</v>
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -26664,17 +27197,14 @@
         <v>9</v>
       </c>
       <c r="B121">
-        <v>89</v>
+        <v>416</v>
       </c>
       <c r="C121">
-        <v>9</v>
-      </c>
-      <c r="D121">
-        <v>11500000</v>
+        <v>5</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -26682,10 +27212,10 @@
         <v>9</v>
       </c>
       <c r="B122">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C122">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D122">
         <v>3100000</v>
@@ -26698,7 +27228,7 @@
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -26706,17 +27236,23 @@
         <v>9</v>
       </c>
       <c r="B123">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="C123">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D123">
-        <v>25000000</v>
+        <v>32000000</v>
+      </c>
+      <c r="F123">
+        <v>32000000</v>
+      </c>
+      <c r="H123">
+        <v>32000000</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -26724,107 +27260,140 @@
         <v>9</v>
       </c>
       <c r="B124">
-        <v>331</v>
+        <v>26</v>
       </c>
       <c r="C124">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D124">
-        <v>12000000</v>
+        <v>12500000</v>
       </c>
       <c r="F124">
-        <v>12000000</v>
+        <v>12500000</v>
       </c>
       <c r="H124">
-        <v>12000000</v>
+        <v>12500000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B125">
+        <v>89</v>
+      </c>
+      <c r="C125">
         <v>9</v>
       </c>
-      <c r="C125">
-        <v>1</v>
+      <c r="D125">
+        <v>11500000</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Walker Kessler</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126">
+        <v>9</v>
+      </c>
+      <c r="B126">
+        <v>167</v>
+      </c>
+      <c r="C126">
         <v>10</v>
       </c>
-      <c r="B126">
-        <v>373</v>
-      </c>
-      <c r="C126">
-        <v>2</v>
+      <c r="D126">
+        <v>3100000</v>
+      </c>
+      <c r="F126">
+        <v>3100000</v>
+      </c>
+      <c r="H126">
+        <v>3100000</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B127">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="C127">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D127">
+        <v>25000000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B128">
-        <v>169</v>
+        <v>331</v>
       </c>
       <c r="C128">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D128">
-        <v>4100000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F128">
+        <v>12000000</v>
+      </c>
+      <c r="H128">
+        <v>12000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Darius Garland</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B129">
-        <v>34</v>
+        <v>433</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D129">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="F129">
-        <v>6000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="H129">
+        <v>1000000</v>
+      </c>
+      <c r="I129" t="s">
+        <v>12</v>
+      </c>
+      <c r="J129">
+        <v>1000000</v>
+      </c>
+      <c r="K129" t="s">
+        <v>12</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Ebuka Okorie</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -26832,17 +27401,14 @@
         <v>10</v>
       </c>
       <c r="B130">
-        <v>168</v>
+        <v>9</v>
       </c>
       <c r="C130">
-        <v>6</v>
-      </c>
-      <c r="D130">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -26850,14 +27416,14 @@
         <v>10</v>
       </c>
       <c r="B131">
-        <v>28</v>
+        <v>373</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -26865,23 +27431,14 @@
         <v>10</v>
       </c>
       <c r="B132">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="C132">
-        <v>8</v>
-      </c>
-      <c r="D132">
-        <v>9250000</v>
-      </c>
-      <c r="F132">
-        <v>10000000</v>
-      </c>
-      <c r="G132" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -26889,23 +27446,17 @@
         <v>10</v>
       </c>
       <c r="B133">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="C133">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D133">
-        <v>15000000</v>
-      </c>
-      <c r="F133">
-        <v>15000000</v>
-      </c>
-      <c r="H133">
-        <v>15000000</v>
+        <v>4100000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -26913,20 +27464,20 @@
         <v>10</v>
       </c>
       <c r="B134">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="C134">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D134">
-        <v>11000000</v>
+        <v>6000000</v>
       </c>
       <c r="F134">
-        <v>11000000</v>
+        <v>6000000</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -26934,23 +27485,17 @@
         <v>10</v>
       </c>
       <c r="B135">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C135">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D135">
-        <v>16000000</v>
-      </c>
-      <c r="F135">
-        <v>16000000</v>
-      </c>
-      <c r="H135">
-        <v>16000000</v>
+        <v>1000000</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -26958,98 +27503,125 @@
         <v>10</v>
       </c>
       <c r="B136">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="C136">
-        <v>12</v>
-      </c>
-      <c r="D136">
-        <v>24000000</v>
+        <v>7</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B137">
-        <v>327</v>
+        <v>44</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D137">
+        <v>9250000</v>
+      </c>
+      <c r="F137">
+        <v>10000000</v>
+      </c>
+      <c r="G137" t="s">
+        <v>12</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B138">
-        <v>213</v>
+        <v>60</v>
       </c>
       <c r="C138">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="D138">
+        <v>15000000</v>
+      </c>
+      <c r="F138">
+        <v>15000000</v>
+      </c>
+      <c r="H138">
+        <v>15000000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B139">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="C139">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D139">
-        <v>1000000</v>
+        <v>11000000</v>
+      </c>
+      <c r="F139">
+        <v>11000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140">
+        <v>10</v>
+      </c>
+      <c r="B140">
+        <v>160</v>
+      </c>
+      <c r="C140">
         <v>11</v>
       </c>
-      <c r="B140">
-        <v>58</v>
-      </c>
-      <c r="C140">
-        <v>4</v>
+      <c r="D140">
+        <v>16000000</v>
+      </c>
+      <c r="F140">
+        <v>16000000</v>
+      </c>
+      <c r="H140">
+        <v>16000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B141">
-        <v>18</v>
+        <v>246</v>
       </c>
       <c r="C141">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D141">
-        <v>1000000</v>
+        <v>24000000</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -27057,14 +27629,14 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>63</v>
+        <v>327</v>
       </c>
       <c r="C142">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -27072,17 +27644,14 @@
         <v>11</v>
       </c>
       <c r="B143">
-        <v>6</v>
+        <v>213</v>
       </c>
       <c r="C143">
-        <v>7</v>
-      </c>
-      <c r="D143">
-        <v>26000000</v>
+        <v>2</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -27090,17 +27659,17 @@
         <v>11</v>
       </c>
       <c r="B144">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="C144">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D144">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -27108,17 +27677,14 @@
         <v>11</v>
       </c>
       <c r="B145">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C145">
-        <v>9</v>
-      </c>
-      <c r="D145">
-        <v>7500000</v>
+        <v>4</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -27126,23 +27692,17 @@
         <v>11</v>
       </c>
       <c r="B146">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="C146">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D146">
-        <v>30000000</v>
-      </c>
-      <c r="F146">
-        <v>30000000</v>
-      </c>
-      <c r="H146">
-        <v>30000000</v>
+        <v>1000000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -27150,17 +27710,14 @@
         <v>11</v>
       </c>
       <c r="B147">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="C147">
-        <v>11</v>
-      </c>
-      <c r="D147">
-        <v>1000000</v>
+        <v>6</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -27168,14 +27725,17 @@
         <v>11</v>
       </c>
       <c r="B148">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="C148">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="D148">
+        <v>26000000</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -27183,14 +27743,17 @@
         <v>11</v>
       </c>
       <c r="B149">
-        <v>266</v>
+        <v>177</v>
       </c>
       <c r="C149">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="D149">
+        <v>15000000</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -27198,128 +27761,137 @@
         <v>11</v>
       </c>
       <c r="B150">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="C150">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="D150">
+        <v>7500000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151">
-        <v>403</v>
+        <v>166</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D151">
-        <v>5000000</v>
+        <v>30000000</v>
       </c>
       <c r="F151">
-        <v>5000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="H151">
+        <v>30000000</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152">
-        <v>345</v>
+        <v>248</v>
       </c>
       <c r="C152">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D152">
-        <v>3500000</v>
-      </c>
-      <c r="F152">
-        <v>3500000</v>
+        <v>1000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
+        <v>11</v>
+      </c>
+      <c r="B153">
+        <v>109</v>
+      </c>
+      <c r="C153">
         <v>12</v>
-      </c>
-      <c r="B153">
-        <v>120</v>
-      </c>
-      <c r="C153">
-        <v>3</v>
-      </c>
-      <c r="D153">
-        <v>1000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B154">
-        <v>22</v>
+        <v>266</v>
       </c>
       <c r="C154">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B155">
-        <v>54</v>
+        <v>195</v>
       </c>
       <c r="C155">
-        <v>5</v>
-      </c>
-      <c r="D155">
-        <v>11000000</v>
+        <v>14</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156">
+        <v>11</v>
+      </c>
+      <c r="B156">
+        <v>436</v>
+      </c>
+      <c r="C156">
+        <v>15</v>
+      </c>
+      <c r="D156">
+        <v>1000000</v>
+      </c>
+      <c r="F156">
+        <v>1000000</v>
+      </c>
+      <c r="H156">
+        <v>1000000</v>
+      </c>
+      <c r="I156" t="s">
         <v>12</v>
       </c>
-      <c r="B156">
-        <v>194</v>
-      </c>
-      <c r="C156">
-        <v>6</v>
-      </c>
-      <c r="D156">
-        <v>20000000</v>
-      </c>
-      <c r="F156">
-        <v>20000000</v>
+      <c r="J156">
+        <v>1000000</v>
+      </c>
+      <c r="K156" t="s">
+        <v>12</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Meleek Thomas</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -27327,23 +27899,20 @@
         <v>12</v>
       </c>
       <c r="B157">
-        <v>226</v>
+        <v>403</v>
       </c>
       <c r="C157">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D157">
-        <v>18000000</v>
+        <v>5000000</v>
       </c>
       <c r="F157">
-        <v>18000000</v>
-      </c>
-      <c r="H157">
-        <v>18000000</v>
+        <v>5000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -27351,17 +27920,20 @@
         <v>12</v>
       </c>
       <c r="B158">
-        <v>115</v>
+        <v>345</v>
       </c>
       <c r="C158">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D158">
-        <v>2500000</v>
+        <v>3500000</v>
+      </c>
+      <c r="F158">
+        <v>3500000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -27369,146 +27941,179 @@
         <v>12</v>
       </c>
       <c r="B159">
-        <v>417</v>
+        <v>120</v>
       </c>
       <c r="C159">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D159">
-        <v>9000000</v>
-      </c>
-      <c r="F159">
-        <v>9500000</v>
-      </c>
-      <c r="H159">
-        <v>10500000</v>
-      </c>
-      <c r="I159" t="s">
-        <v>12</v>
-      </c>
-      <c r="J159">
-        <v>11500000</v>
+        <v>1000000</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>A.J. Dybantsa</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B160">
-        <v>307</v>
+        <v>22</v>
       </c>
       <c r="C160">
-        <v>1</v>
-      </c>
-      <c r="D160">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B161">
-        <v>363</v>
+        <v>54</v>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D161">
+        <v>11000000</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B162">
-        <v>296</v>
+        <v>194</v>
       </c>
       <c r="C162">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D162">
-        <v>3000000</v>
+        <v>20000000</v>
+      </c>
+      <c r="F162">
+        <v>20000000</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B163">
-        <v>171</v>
+        <v>226</v>
       </c>
       <c r="C163">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D163">
-        <v>2000000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F163">
+        <v>18000000</v>
+      </c>
+      <c r="H163">
+        <v>18000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B164">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="C164">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D164">
+        <v>2500000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B165">
-        <v>46</v>
+        <v>417</v>
       </c>
       <c r="C165">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D165">
+        <v>9000000</v>
+      </c>
+      <c r="F165">
+        <v>9500000</v>
+      </c>
+      <c r="H165">
+        <v>10500000</v>
+      </c>
+      <c r="I165" t="s">
+        <v>12</v>
+      </c>
+      <c r="J165">
+        <v>11500000</v>
+      </c>
+      <c r="K165" t="s">
+        <v>12</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B166">
-        <v>4</v>
+        <v>431</v>
       </c>
       <c r="C166">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D166">
-        <v>11500000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F166">
+        <v>1000000</v>
+      </c>
+      <c r="H166">
+        <v>1000000</v>
+      </c>
+      <c r="I166" t="s">
+        <v>12</v>
+      </c>
+      <c r="J166">
+        <v>1000000</v>
+      </c>
+      <c r="K166" t="s">
+        <v>12</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Nate Ament</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -27516,23 +28121,17 @@
         <v>13</v>
       </c>
       <c r="B167">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="C167">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D167">
-        <v>16000000</v>
-      </c>
-      <c r="F167">
-        <v>16000000</v>
-      </c>
-      <c r="H167">
-        <v>16000000</v>
+        <v>1000000</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -27540,23 +28139,14 @@
         <v>13</v>
       </c>
       <c r="B168">
-        <v>55</v>
+        <v>363</v>
       </c>
       <c r="C168">
-        <v>9</v>
-      </c>
-      <c r="D168">
-        <v>12000000</v>
-      </c>
-      <c r="F168">
-        <v>12000000</v>
-      </c>
-      <c r="H168">
-        <v>12000000</v>
+        <v>2</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -27564,17 +28154,17 @@
         <v>13</v>
       </c>
       <c r="B169">
-        <v>66</v>
+        <v>296</v>
       </c>
       <c r="C169">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D169">
-        <v>19000000</v>
+        <v>3000000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -27582,161 +28172,188 @@
         <v>13</v>
       </c>
       <c r="B170">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C170">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D170">
-        <v>6000000</v>
-      </c>
-      <c r="F170">
-        <v>6000000</v>
-      </c>
-      <c r="H170">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B171">
-        <v>317</v>
+        <v>10</v>
       </c>
       <c r="C171">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B172">
-        <v>299</v>
+        <v>46</v>
       </c>
       <c r="C172">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B173">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="C173">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="D173">
+        <v>11500000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B174">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="C174">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="D174">
+        <v>16000000</v>
+      </c>
+      <c r="F174">
+        <v>16000000</v>
+      </c>
+      <c r="H174">
+        <v>16000000</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B175">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C175">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D175">
-        <v>1000000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F175">
+        <v>12000000</v>
+      </c>
+      <c r="H175">
+        <v>12000000</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B176">
-        <v>238</v>
+        <v>66</v>
       </c>
       <c r="C176">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D176">
-        <v>3000000</v>
+        <v>19000000</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B177">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="C177">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D177">
-        <v>20500000</v>
+        <v>6000000</v>
       </c>
       <c r="F177">
-        <v>20500000</v>
+        <v>6000000</v>
       </c>
       <c r="H177">
-        <v>20500000</v>
+        <v>6000000</v>
       </c>
       <c r="L177" t="str">
         <f>VLOOKUP(B177,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B178">
-        <v>73</v>
+        <v>430</v>
       </c>
       <c r="C178">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D178">
-        <v>19500000</v>
+        <v>2600000</v>
+      </c>
+      <c r="F178">
+        <v>2800000</v>
+      </c>
+      <c r="H178">
+        <v>3000000</v>
+      </c>
+      <c r="I178" t="s">
+        <v>12</v>
+      </c>
+      <c r="J178">
+        <v>3300000</v>
+      </c>
+      <c r="K178" t="s">
+        <v>12</v>
       </c>
       <c r="L178" t="str">
         <f>VLOOKUP(B178,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Cameron Carr</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -27744,29 +28361,14 @@
         <v>14</v>
       </c>
       <c r="B179">
-        <v>61</v>
+        <v>317</v>
       </c>
       <c r="C179">
-        <v>9</v>
-      </c>
-      <c r="D179">
-        <v>9500000</v>
-      </c>
-      <c r="F179">
-        <v>10500000</v>
-      </c>
-      <c r="G179" t="s">
-        <v>12</v>
-      </c>
-      <c r="H179">
-        <v>11500000</v>
-      </c>
-      <c r="I179" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L179" t="str">
         <f>VLOOKUP(B179,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -27774,14 +28376,14 @@
         <v>14</v>
       </c>
       <c r="B180">
+        <v>299</v>
+      </c>
+      <c r="C180">
         <v>2</v>
-      </c>
-      <c r="C180">
-        <v>10</v>
       </c>
       <c r="L180" t="str">
         <f>VLOOKUP(B180,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -27789,14 +28391,14 @@
         <v>14</v>
       </c>
       <c r="B181">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="C181">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L181" t="str">
         <f>VLOOKUP(B181,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -27804,23 +28406,14 @@
         <v>14</v>
       </c>
       <c r="B182">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="C182">
-        <v>12</v>
-      </c>
-      <c r="D182">
-        <v>20000000</v>
-      </c>
-      <c r="F182">
-        <v>20000000</v>
-      </c>
-      <c r="H182">
-        <v>20000000</v>
+        <v>4</v>
       </c>
       <c r="L182" t="str">
         <f>VLOOKUP(B182,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -27828,52 +28421,214 @@
         <v>14</v>
       </c>
       <c r="B183">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="C183">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D183">
-        <v>3200000</v>
-      </c>
-      <c r="F183">
-        <v>3500000</v>
+        <v>1000000</v>
       </c>
       <c r="L183" t="str">
         <f>VLOOKUP(B183,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B184">
-        <v>426</v>
+        <v>238</v>
       </c>
       <c r="C184">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D184">
-        <v>3400000</v>
-      </c>
-      <c r="F184">
-        <v>3600000</v>
-      </c>
-      <c r="H184">
-        <v>3800000</v>
-      </c>
-      <c r="I184" t="s">
-        <v>12</v>
-      </c>
-      <c r="J184">
-        <v>4100000</v>
-      </c>
-      <c r="K184" t="s">
-        <v>12</v>
+        <v>3000000</v>
       </c>
       <c r="L184" t="str">
         <f>VLOOKUP(B184,players!A:B,2)</f>
+        <v>Coby White</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>14</v>
+      </c>
+      <c r="B185">
+        <v>19</v>
+      </c>
+      <c r="C185">
+        <v>7</v>
+      </c>
+      <c r="D185">
+        <v>20500000</v>
+      </c>
+      <c r="F185">
+        <v>20500000</v>
+      </c>
+      <c r="H185">
+        <v>20500000</v>
+      </c>
+      <c r="L185" t="str">
+        <f>VLOOKUP(B185,players!A:B,2)</f>
+        <v>Evan Mobley</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>14</v>
+      </c>
+      <c r="B186">
+        <v>73</v>
+      </c>
+      <c r="C186">
+        <v>8</v>
+      </c>
+      <c r="D186">
+        <v>19500000</v>
+      </c>
+      <c r="L186" t="str">
+        <f>VLOOKUP(B186,players!A:B,2)</f>
+        <v>LeBron James</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>14</v>
+      </c>
+      <c r="B187">
+        <v>61</v>
+      </c>
+      <c r="C187">
+        <v>9</v>
+      </c>
+      <c r="D187">
+        <v>9500000</v>
+      </c>
+      <c r="F187">
+        <v>10500000</v>
+      </c>
+      <c r="G187" t="s">
+        <v>12</v>
+      </c>
+      <c r="H187">
+        <v>11500000</v>
+      </c>
+      <c r="I187" t="s">
+        <v>12</v>
+      </c>
+      <c r="L187" t="str">
+        <f>VLOOKUP(B187,players!A:B,2)</f>
+        <v>Cooper Flagg</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>14</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188">
+        <v>10</v>
+      </c>
+      <c r="L188" t="str">
+        <f>VLOOKUP(B188,players!A:B,2)</f>
+        <v>Karl-Anthony Towns</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>14</v>
+      </c>
+      <c r="B189">
+        <v>220</v>
+      </c>
+      <c r="C189">
+        <v>11</v>
+      </c>
+      <c r="L189" t="str">
+        <f>VLOOKUP(B189,players!A:B,2)</f>
+        <v>Quentin Grimes</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>14</v>
+      </c>
+      <c r="B190">
+        <v>145</v>
+      </c>
+      <c r="C190">
+        <v>12</v>
+      </c>
+      <c r="D190">
+        <v>20000000</v>
+      </c>
+      <c r="F190">
+        <v>20000000</v>
+      </c>
+      <c r="H190">
+        <v>20000000</v>
+      </c>
+      <c r="L190" t="str">
+        <f>VLOOKUP(B190,players!A:B,2)</f>
+        <v>LaMelo Ball</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>14</v>
+      </c>
+      <c r="B191">
+        <v>273</v>
+      </c>
+      <c r="C191">
+        <v>13</v>
+      </c>
+      <c r="D191">
+        <v>3200000</v>
+      </c>
+      <c r="F191">
+        <v>3500000</v>
+      </c>
+      <c r="L191" t="str">
+        <f>VLOOKUP(B191,players!A:B,2)</f>
+        <v>Cason Wallace</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>13</v>
+      </c>
+      <c r="B192">
+        <v>426</v>
+      </c>
+      <c r="C192">
+        <v>14</v>
+      </c>
+      <c r="D192">
+        <v>3400000</v>
+      </c>
+      <c r="F192">
+        <v>3600000</v>
+      </c>
+      <c r="H192">
+        <v>3800000</v>
+      </c>
+      <c r="I192" t="s">
+        <v>12</v>
+      </c>
+      <c r="J192">
+        <v>4100000</v>
+      </c>
+      <c r="K192" t="s">
+        <v>12</v>
+      </c>
+      <c r="L192" t="str">
+        <f>VLOOKUP(B192,players!A:B,2)</f>
         <v>Morez Johnson Jr.</v>
       </c>
     </row>

--- a/Fantasy unificado/roster.xlsx
+++ b/Fantasy unificado/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43C45123-7EB4-477F-8C0F-7C1A0BE0E23E}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01B9AC82-2A8E-4FB0-8D2D-605EB5BAE309}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="E145" s="1">
         <v>20.5</v>
@@ -12948,7 +12948,7 @@
         <v>353</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="E321" s="1">
         <v>11.1</v>
@@ -22993,7 +22993,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -24664,6 +24664,11 @@
       </c>
       <c r="H58" t="s">
         <v>516</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Fantasy unificado/roster.xlsx
+++ b/Fantasy unificado/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01B9AC82-2A8E-4FB0-8D2D-605EB5BAE309}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="11_1C3098EE5E7872337143A0BEC13924F4E4C08868" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD5950F-F7EF-43C9-858B-CF72F6F39398}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="729">
   <si>
     <t>team_id</t>
   </si>
@@ -22070,7 +22070,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -22983,6 +22983,58 @@
         <v>588</v>
       </c>
       <c r="H35" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>504</v>
+      </c>
+      <c r="C36" t="s">
+        <v>586</v>
+      </c>
+      <c r="D36" t="s">
+        <v>587</v>
+      </c>
+      <c r="E36">
+        <v>7</v>
+      </c>
+      <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36" t="s">
+        <v>588</v>
+      </c>
+      <c r="H36" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>503</v>
+      </c>
+      <c r="C37" t="s">
+        <v>586</v>
+      </c>
+      <c r="D37" t="s">
+        <v>587</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>588</v>
+      </c>
+      <c r="H37" t="s">
         <v>589</v>
       </c>
     </row>
@@ -22993,8 +23045,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -24547,6 +24602,9 @@
       <c r="H53" t="s">
         <v>516</v>
       </c>
+      <c r="I53" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
@@ -24567,6 +24625,9 @@
       <c r="F54">
         <v>1</v>
       </c>
+      <c r="I54" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
@@ -24592,6 +24653,9 @@
       </c>
       <c r="H55" t="s">
         <v>516</v>
+      </c>
+      <c r="I55" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -24613,6 +24677,9 @@
       <c r="F56">
         <v>1</v>
       </c>
+      <c r="I56" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
@@ -24639,6 +24706,9 @@
       <c r="H57" t="s">
         <v>519</v>
       </c>
+      <c r="I57" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
@@ -24665,10 +24735,170 @@
       <c r="H58" t="s">
         <v>516</v>
       </c>
+      <c r="I58" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>595</v>
+      </c>
+      <c r="D59" t="s">
+        <v>604</v>
+      </c>
+      <c r="E59">
+        <v>5</v>
+      </c>
+      <c r="F59">
+        <v>7</v>
+      </c>
+      <c r="I59" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
+        <v>595</v>
+      </c>
+      <c r="D60" t="s">
+        <v>598</v>
+      </c>
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="F60">
+        <v>7</v>
+      </c>
+      <c r="I60" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>6</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>599</v>
+      </c>
+      <c r="D61">
+        <v>49</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61" t="s">
+        <v>605</v>
+      </c>
+      <c r="H61" t="s">
+        <v>600</v>
+      </c>
+      <c r="I61" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>6</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>599</v>
+      </c>
+      <c r="D62">
+        <v>423</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>516</v>
+      </c>
+      <c r="H62" t="s">
+        <v>519</v>
+      </c>
+      <c r="I62" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>599</v>
+      </c>
+      <c r="D63">
+        <v>435</v>
+      </c>
+      <c r="E63">
+        <v>7</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
+        <v>516</v>
+      </c>
+      <c r="H63" t="s">
+        <v>519</v>
+      </c>
+      <c r="I63" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>599</v>
+      </c>
+      <c r="D64">
+        <v>437</v>
+      </c>
+      <c r="E64">
+        <v>7</v>
+      </c>
+      <c r="F64">
+        <v>7</v>
+      </c>
+      <c r="G64" t="s">
+        <v>516</v>
+      </c>
+      <c r="H64" t="s">
+        <v>519</v>
+      </c>
+      <c r="I64" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>
